--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -559,7 +559,7 @@
         <v>5.4143</v>
       </c>
       <c r="F6" t="n">
-        <v>5.1237</v>
+        <v>5.1259</v>
       </c>
     </row>
     <row r="7">
@@ -581,7 +581,7 @@
         <v>6.2785</v>
       </c>
       <c r="F7" t="n">
-        <v>5.9496</v>
+        <v>5.9594</v>
       </c>
     </row>
     <row r="8">
@@ -735,7 +735,7 @@
         <v>1256</v>
       </c>
       <c r="F14" t="n">
-        <v>1309.75</v>
+        <v>1293.75</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +757,7 @@
         <v>536.75</v>
       </c>
       <c r="F15" t="n">
-        <v>536.75</v>
+        <v>512</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -581,7 +581,7 @@
         <v>6.2785</v>
       </c>
       <c r="F7" t="n">
-        <v>5.9594</v>
+        <v>5.9606</v>
       </c>
     </row>
     <row r="8">

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -471,7 +471,7 @@
         <v>110979</v>
       </c>
       <c r="F2" t="n">
-        <v>185147</v>
+        <v>188913.453125</v>
       </c>
     </row>
     <row r="3">
@@ -493,7 +493,7 @@
         <v>106.489998</v>
       </c>
       <c r="F3" t="n">
-        <v>181.940002</v>
+        <v>186.029999</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>127.400002</v>
       </c>
       <c r="F4" t="n">
-        <v>110.989998</v>
+        <v>112.760002</v>
       </c>
     </row>
     <row r="5">
@@ -537,7 +537,7 @@
         <v>255</v>
       </c>
       <c r="F5" t="n">
-        <v>447.350006</v>
+        <v>439.269989</v>
       </c>
     </row>
     <row r="6">
@@ -559,7 +559,7 @@
         <v>5.4143</v>
       </c>
       <c r="F6" t="n">
-        <v>5.1259</v>
+        <v>5.0806</v>
       </c>
     </row>
     <row r="7">
@@ -581,7 +581,7 @@
         <v>6.2785</v>
       </c>
       <c r="F7" t="n">
-        <v>5.9606</v>
+        <v>5.9044</v>
       </c>
     </row>
     <row r="8">
@@ -603,7 +603,7 @@
         <v>4307.540039</v>
       </c>
       <c r="F8" t="n">
-        <v>7718.600098</v>
+        <v>7684.339844</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         <v>14448.580078</v>
       </c>
       <c r="F9" t="n">
-        <v>26506.990234</v>
+        <v>26390.132812</v>
       </c>
     </row>
     <row r="10">
@@ -647,7 +647,7 @@
         <v>33843.921875</v>
       </c>
       <c r="F10" t="n">
-        <v>53414.25</v>
+        <v>52819.558594</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>1755.300049</v>
       </c>
       <c r="F11" t="n">
-        <v>4476.600098</v>
+        <v>4442</v>
       </c>
     </row>
     <row r="12">
@@ -691,7 +691,7 @@
         <v>75.029999</v>
       </c>
       <c r="F12" t="n">
-        <v>91.480003</v>
+        <v>93.269997</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>78.519997</v>
       </c>
       <c r="F13" t="n">
-        <v>96.279999</v>
+        <v>98.08000199999999</v>
       </c>
     </row>
     <row r="14">
@@ -735,7 +735,7 @@
         <v>1256</v>
       </c>
       <c r="F14" t="n">
-        <v>1293.75</v>
+        <v>1307.25</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +757,7 @@
         <v>536.75</v>
       </c>
       <c r="F15" t="n">
-        <v>512</v>
+        <v>535.5</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -471,7 +471,7 @@
         <v>110979</v>
       </c>
       <c r="F2" t="n">
-        <v>188913.453125</v>
+        <v>187042.90625</v>
       </c>
     </row>
     <row r="3">
@@ -493,7 +493,7 @@
         <v>106.489998</v>
       </c>
       <c r="F3" t="n">
-        <v>186.029999</v>
+        <v>184.070007</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>127.400002</v>
       </c>
       <c r="F4" t="n">
-        <v>112.760002</v>
+        <v>111.110001</v>
       </c>
     </row>
     <row r="5">
@@ -537,7 +537,7 @@
         <v>255</v>
       </c>
       <c r="F5" t="n">
-        <v>439.269989</v>
+        <v>440.329987</v>
       </c>
     </row>
     <row r="6">
@@ -559,7 +559,7 @@
         <v>5.4143</v>
       </c>
       <c r="F6" t="n">
-        <v>5.0806</v>
+        <v>5.0937</v>
       </c>
     </row>
     <row r="7">
@@ -581,7 +581,7 @@
         <v>6.2785</v>
       </c>
       <c r="F7" t="n">
-        <v>5.9044</v>
+        <v>5.9353</v>
       </c>
     </row>
     <row r="8">
@@ -603,7 +603,7 @@
         <v>4307.540039</v>
       </c>
       <c r="F8" t="n">
-        <v>7684.339844</v>
+        <v>7653.459961</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         <v>14448.580078</v>
       </c>
       <c r="F9" t="n">
-        <v>26390.132812</v>
+        <v>26360.449219</v>
       </c>
     </row>
     <row r="10">
@@ -647,7 +647,7 @@
         <v>33843.921875</v>
       </c>
       <c r="F10" t="n">
-        <v>52819.558594</v>
+        <v>52381.640625</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>1755.300049</v>
       </c>
       <c r="F11" t="n">
-        <v>4442</v>
+        <v>4456.600098</v>
       </c>
     </row>
     <row r="12">
@@ -691,7 +691,7 @@
         <v>75.029999</v>
       </c>
       <c r="F12" t="n">
-        <v>93.269997</v>
+        <v>95.75</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>78.519997</v>
       </c>
       <c r="F13" t="n">
-        <v>98.08000199999999</v>
+        <v>100.669998</v>
       </c>
     </row>
     <row r="14">
@@ -735,7 +735,7 @@
         <v>1256</v>
       </c>
       <c r="F14" t="n">
-        <v>1307.25</v>
+        <v>1308.75</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +757,7 @@
         <v>536.75</v>
       </c>
       <c r="F15" t="n">
-        <v>535.5</v>
+        <v>527.25</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -471,7 +471,7 @@
         <v>110979</v>
       </c>
       <c r="F2" t="n">
-        <v>187042.90625</v>
+        <v>185144.859375</v>
       </c>
     </row>
     <row r="3">
@@ -493,7 +493,7 @@
         <v>106.489998</v>
       </c>
       <c r="F3" t="n">
-        <v>184.070007</v>
+        <v>182.330002</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>127.400002</v>
       </c>
       <c r="F4" t="n">
-        <v>111.110001</v>
+        <v>109.870003</v>
       </c>
     </row>
     <row r="5">
@@ -537,7 +537,7 @@
         <v>255</v>
       </c>
       <c r="F5" t="n">
-        <v>440.329987</v>
+        <v>440.929993</v>
       </c>
     </row>
     <row r="6">
@@ -559,7 +559,7 @@
         <v>5.4143</v>
       </c>
       <c r="F6" t="n">
-        <v>5.0937</v>
+        <v>5.1422</v>
       </c>
     </row>
     <row r="7">
@@ -581,7 +581,7 @@
         <v>6.2785</v>
       </c>
       <c r="F7" t="n">
-        <v>5.9353</v>
+        <v>5.9703</v>
       </c>
     </row>
     <row r="8">
@@ -603,7 +603,7 @@
         <v>4307.540039</v>
       </c>
       <c r="F8" t="n">
-        <v>7653.459961</v>
+        <v>7583.859863</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         <v>14448.580078</v>
       </c>
       <c r="F9" t="n">
-        <v>26360.449219</v>
+        <v>26037.785156</v>
       </c>
     </row>
     <row r="10">
@@ -647,7 +647,7 @@
         <v>33843.921875</v>
       </c>
       <c r="F10" t="n">
-        <v>52381.640625</v>
+        <v>52079.46875</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>1755.300049</v>
       </c>
       <c r="F11" t="n">
-        <v>4456.600098</v>
+        <v>4409.5</v>
       </c>
     </row>
     <row r="12">
@@ -691,7 +691,7 @@
         <v>75.029999</v>
       </c>
       <c r="F12" t="n">
-        <v>95.75</v>
+        <v>99.300003</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>78.519997</v>
       </c>
       <c r="F13" t="n">
-        <v>100.669998</v>
+        <v>104.540001</v>
       </c>
     </row>
     <row r="14">
@@ -735,7 +735,7 @@
         <v>1256</v>
       </c>
       <c r="F14" t="n">
-        <v>1308.75</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +757,7 @@
         <v>536.75</v>
       </c>
       <c r="F15" t="n">
-        <v>527.25</v>
+        <v>528</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -471,7 +471,7 @@
         <v>110979</v>
       </c>
       <c r="F2" t="n">
-        <v>185144.859375</v>
+        <v>187021.609375</v>
       </c>
     </row>
     <row r="3">
@@ -493,7 +493,7 @@
         <v>106.489998</v>
       </c>
       <c r="F3" t="n">
-        <v>182.330002</v>
+        <v>184.119995</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>127.400002</v>
       </c>
       <c r="F4" t="n">
-        <v>109.870003</v>
+        <v>111.400002</v>
       </c>
     </row>
     <row r="5">
@@ -537,7 +537,7 @@
         <v>255</v>
       </c>
       <c r="F5" t="n">
-        <v>440.929993</v>
+        <v>440.160004</v>
       </c>
     </row>
     <row r="6">
@@ -559,7 +559,7 @@
         <v>5.4143</v>
       </c>
       <c r="F6" t="n">
-        <v>5.1422</v>
+        <v>5.083</v>
       </c>
     </row>
     <row r="7">
@@ -581,7 +581,7 @@
         <v>6.2785</v>
       </c>
       <c r="F7" t="n">
-        <v>5.9703</v>
+        <v>5.9061</v>
       </c>
     </row>
     <row r="8">
@@ -603,7 +603,7 @@
         <v>4307.540039</v>
       </c>
       <c r="F8" t="n">
-        <v>7583.859863</v>
+        <v>7675.77002</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         <v>14448.580078</v>
       </c>
       <c r="F9" t="n">
-        <v>26037.785156</v>
+        <v>26405.673828</v>
       </c>
     </row>
     <row r="10">
@@ -647,7 +647,7 @@
         <v>33843.921875</v>
       </c>
       <c r="F10" t="n">
-        <v>52079.46875</v>
+        <v>52662.679688</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>1755.300049</v>
       </c>
       <c r="F11" t="n">
-        <v>4409.5</v>
+        <v>4432.399902</v>
       </c>
     </row>
     <row r="12">
@@ -691,7 +691,7 @@
         <v>75.029999</v>
       </c>
       <c r="F12" t="n">
-        <v>99.300003</v>
+        <v>98.75</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>78.519997</v>
       </c>
       <c r="F13" t="n">
-        <v>104.540001</v>
+        <v>104.110001</v>
       </c>
     </row>
     <row r="14">
@@ -735,7 +735,7 @@
         <v>1256</v>
       </c>
       <c r="F14" t="n">
-        <v>1316</v>
+        <v>1311.5</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +757,7 @@
         <v>536.75</v>
       </c>
       <c r="F15" t="n">
-        <v>528</v>
+        <v>525.5</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -471,7 +471,7 @@
         <v>110979</v>
       </c>
       <c r="F2" t="n">
-        <v>187021.609375</v>
+        <v>187039.734375</v>
       </c>
     </row>
     <row r="3">
@@ -493,7 +493,7 @@
         <v>106.489998</v>
       </c>
       <c r="F3" t="n">
-        <v>184.119995</v>
+        <v>184.139999</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>127.400002</v>
       </c>
       <c r="F4" t="n">
-        <v>111.400002</v>
+        <v>111.370003</v>
       </c>
     </row>
     <row r="5">
@@ -537,7 +537,7 @@
         <v>255</v>
       </c>
       <c r="F5" t="n">
-        <v>440.160004</v>
+        <v>440.209991</v>
       </c>
     </row>
     <row r="6">
@@ -559,7 +559,7 @@
         <v>5.4143</v>
       </c>
       <c r="F6" t="n">
-        <v>5.083</v>
+        <v>5.0901</v>
       </c>
     </row>
     <row r="7">
@@ -581,7 +581,7 @@
         <v>6.2785</v>
       </c>
       <c r="F7" t="n">
-        <v>5.9061</v>
+        <v>5.9107</v>
       </c>
     </row>
     <row r="8">
@@ -603,7 +603,7 @@
         <v>4307.540039</v>
       </c>
       <c r="F8" t="n">
-        <v>7675.77002</v>
+        <v>7664.779785</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         <v>14448.580078</v>
       </c>
       <c r="F9" t="n">
-        <v>26405.673828</v>
+        <v>26356.910156</v>
       </c>
     </row>
     <row r="10">
@@ -647,7 +647,7 @@
         <v>33843.921875</v>
       </c>
       <c r="F10" t="n">
-        <v>52662.679688</v>
+        <v>52650.328125</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>1755.300049</v>
       </c>
       <c r="F11" t="n">
-        <v>4432.399902</v>
+        <v>4430.5</v>
       </c>
     </row>
     <row r="12">
@@ -691,7 +691,7 @@
         <v>75.029999</v>
       </c>
       <c r="F12" t="n">
-        <v>98.75</v>
+        <v>99.050003</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>78.519997</v>
       </c>
       <c r="F13" t="n">
-        <v>104.110001</v>
+        <v>104.43</v>
       </c>
     </row>
     <row r="14">
@@ -735,7 +735,7 @@
         <v>1256</v>
       </c>
       <c r="F14" t="n">
-        <v>1311.5</v>
+        <v>1310.75</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +757,7 @@
         <v>536.75</v>
       </c>
       <c r="F15" t="n">
-        <v>525.5</v>
+        <v>525.25</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -471,7 +471,7 @@
         <v>110979</v>
       </c>
       <c r="F2" t="n">
-        <v>187039.734375</v>
+        <v>187207</v>
       </c>
     </row>
     <row r="3">
@@ -493,7 +493,7 @@
         <v>106.489998</v>
       </c>
       <c r="F3" t="n">
-        <v>184.139999</v>
+        <v>185.210007</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>127.400002</v>
       </c>
       <c r="F4" t="n">
-        <v>111.370003</v>
+        <v>112.300003</v>
       </c>
     </row>
     <row r="5">
@@ -537,7 +537,7 @@
         <v>255</v>
       </c>
       <c r="F5" t="n">
-        <v>440.209991</v>
+        <v>437.649994</v>
       </c>
     </row>
     <row r="6">
@@ -559,7 +559,7 @@
         <v>5.4143</v>
       </c>
       <c r="F6" t="n">
-        <v>5.0901</v>
+        <v>5.1262</v>
       </c>
     </row>
     <row r="7">
@@ -581,7 +581,7 @@
         <v>6.2785</v>
       </c>
       <c r="F7" t="n">
-        <v>5.9107</v>
+        <v>5.9463</v>
       </c>
     </row>
     <row r="8">
@@ -603,7 +603,7 @@
         <v>4307.540039</v>
       </c>
       <c r="F8" t="n">
-        <v>7664.779785</v>
+        <v>7656.97998</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         <v>14448.580078</v>
       </c>
       <c r="F9" t="n">
-        <v>26356.910156</v>
+        <v>26333.039062</v>
       </c>
     </row>
     <row r="10">
@@ -647,7 +647,7 @@
         <v>33843.921875</v>
       </c>
       <c r="F10" t="n">
-        <v>52650.328125</v>
+        <v>52573.289062</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>1755.300049</v>
       </c>
       <c r="F11" t="n">
-        <v>4430.5</v>
+        <v>4366.200195</v>
       </c>
     </row>
     <row r="12">
@@ -691,7 +691,7 @@
         <v>75.029999</v>
       </c>
       <c r="F12" t="n">
-        <v>99.050003</v>
+        <v>100.050003</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>78.519997</v>
       </c>
       <c r="F13" t="n">
-        <v>104.43</v>
+        <v>104.610001</v>
       </c>
     </row>
     <row r="14">
@@ -735,7 +735,7 @@
         <v>1256</v>
       </c>
       <c r="F14" t="n">
-        <v>1310.75</v>
+        <v>1280.25</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +757,7 @@
         <v>536.75</v>
       </c>
       <c r="F15" t="n">
-        <v>525.25</v>
+        <v>510.25</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -493,7 +493,7 @@
         <v>106.489998</v>
       </c>
       <c r="F3" t="n">
-        <v>185.210007</v>
+        <v>183.850006</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>127.400002</v>
       </c>
       <c r="F4" t="n">
-        <v>112.300003</v>
+        <v>110.830002</v>
       </c>
     </row>
     <row r="5">
@@ -537,7 +537,7 @@
         <v>255</v>
       </c>
       <c r="F5" t="n">
-        <v>437.649994</v>
+        <v>443.149994</v>
       </c>
     </row>
     <row r="6">
@@ -669,7 +669,7 @@
         <v>1755.300049</v>
       </c>
       <c r="F11" t="n">
-        <v>4366.200195</v>
+        <v>4408.899902</v>
       </c>
     </row>
     <row r="12">
@@ -735,7 +735,7 @@
         <v>1256</v>
       </c>
       <c r="F14" t="n">
-        <v>1280.25</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +757,7 @@
         <v>536.75</v>
       </c>
       <c r="F15" t="n">
-        <v>510.25</v>
+        <v>532</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -471,7 +471,7 @@
         <v>110979</v>
       </c>
       <c r="F2" t="n">
-        <v>187207</v>
+        <v>185371.140625</v>
       </c>
     </row>
     <row r="3">
@@ -493,7 +493,7 @@
         <v>106.489998</v>
       </c>
       <c r="F3" t="n">
-        <v>183.850006</v>
+        <v>182.369995</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>127.400002</v>
       </c>
       <c r="F4" t="n">
-        <v>110.830002</v>
+        <v>109.68</v>
       </c>
     </row>
     <row r="5">
@@ -537,7 +537,7 @@
         <v>255</v>
       </c>
       <c r="F5" t="n">
-        <v>443.149994</v>
+        <v>443.630005</v>
       </c>
     </row>
     <row r="6">
@@ -559,7 +559,7 @@
         <v>5.4143</v>
       </c>
       <c r="F6" t="n">
-        <v>5.1262</v>
+        <v>5.1539</v>
       </c>
     </row>
     <row r="7">
@@ -581,7 +581,7 @@
         <v>6.2785</v>
       </c>
       <c r="F7" t="n">
-        <v>5.9463</v>
+        <v>5.9512</v>
       </c>
     </row>
     <row r="8">
@@ -603,7 +603,7 @@
         <v>4307.540039</v>
       </c>
       <c r="F8" t="n">
-        <v>7656.97998</v>
+        <v>7626.77002</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         <v>14448.580078</v>
       </c>
       <c r="F9" t="n">
-        <v>26333.039062</v>
+        <v>26209.451172</v>
       </c>
     </row>
     <row r="10">
@@ -647,7 +647,7 @@
         <v>33843.921875</v>
       </c>
       <c r="F10" t="n">
-        <v>52573.289062</v>
+        <v>52482.101562</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>1755.300049</v>
       </c>
       <c r="F11" t="n">
-        <v>4408.899902</v>
+        <v>4331.600098</v>
       </c>
     </row>
     <row r="12">
@@ -691,7 +691,7 @@
         <v>75.029999</v>
       </c>
       <c r="F12" t="n">
-        <v>100.050003</v>
+        <v>102.970001</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>78.519997</v>
       </c>
       <c r="F13" t="n">
-        <v>104.610001</v>
+        <v>107.419998</v>
       </c>
     </row>
     <row r="14">
@@ -735,7 +735,7 @@
         <v>1256</v>
       </c>
       <c r="F14" t="n">
-        <v>1299</v>
+        <v>1306.5</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +757,7 @@
         <v>536.75</v>
       </c>
       <c r="F15" t="n">
-        <v>532</v>
+        <v>530.5</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -471,7 +471,7 @@
         <v>110979</v>
       </c>
       <c r="F2" t="n">
-        <v>185371.140625</v>
+        <v>185959.625</v>
       </c>
     </row>
     <row r="3">
@@ -493,7 +493,7 @@
         <v>106.489998</v>
       </c>
       <c r="F3" t="n">
-        <v>182.369995</v>
+        <v>183.039993</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>127.400002</v>
       </c>
       <c r="F4" t="n">
-        <v>109.68</v>
+        <v>109.540001</v>
       </c>
     </row>
     <row r="5">
@@ -537,7 +537,7 @@
         <v>255</v>
       </c>
       <c r="F5" t="n">
-        <v>443.630005</v>
+        <v>440.839996</v>
       </c>
     </row>
     <row r="6">
@@ -559,7 +559,7 @@
         <v>5.4143</v>
       </c>
       <c r="F6" t="n">
-        <v>5.1539</v>
+        <v>5.1456</v>
       </c>
     </row>
     <row r="7">
@@ -581,7 +581,7 @@
         <v>6.2785</v>
       </c>
       <c r="F7" t="n">
-        <v>5.9512</v>
+        <v>5.9456</v>
       </c>
     </row>
     <row r="8">
@@ -603,7 +603,7 @@
         <v>4307.540039</v>
       </c>
       <c r="F8" t="n">
-        <v>7626.77002</v>
+        <v>7585.890137</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         <v>14448.580078</v>
       </c>
       <c r="F9" t="n">
-        <v>26209.451172</v>
+        <v>26026.601562</v>
       </c>
     </row>
     <row r="10">
@@ -647,7 +647,7 @@
         <v>33843.921875</v>
       </c>
       <c r="F10" t="n">
-        <v>52482.101562</v>
+        <v>51923.578125</v>
       </c>
     </row>
     <row r="11">
@@ -666,10 +666,10 @@
         <v>61</v>
       </c>
       <c r="E11" t="n">
-        <v>1755.300049</v>
+        <v>1757</v>
       </c>
       <c r="F11" t="n">
-        <v>4331.600098</v>
+        <v>4329.299805</v>
       </c>
     </row>
     <row r="12">
@@ -691,7 +691,7 @@
         <v>75.029999</v>
       </c>
       <c r="F12" t="n">
-        <v>102.970001</v>
+        <v>103.730003</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>78.519997</v>
       </c>
       <c r="F13" t="n">
-        <v>107.419998</v>
+        <v>102.610001</v>
       </c>
     </row>
     <row r="14">
@@ -757,7 +757,7 @@
         <v>536.75</v>
       </c>
       <c r="F15" t="n">
-        <v>530.5</v>
+        <v>531.25</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -471,7 +471,7 @@
         <v>110979</v>
       </c>
       <c r="F2" t="n">
-        <v>185959.625</v>
+        <v>185399.484375</v>
       </c>
     </row>
     <row r="3">
@@ -493,7 +493,7 @@
         <v>106.489998</v>
       </c>
       <c r="F3" t="n">
-        <v>183.039993</v>
+        <v>182.539993</v>
       </c>
     </row>
     <row r="4">
@@ -537,7 +537,7 @@
         <v>255</v>
       </c>
       <c r="F5" t="n">
-        <v>440.839996</v>
+        <v>442.51001</v>
       </c>
     </row>
     <row r="6">
@@ -559,7 +559,7 @@
         <v>5.4143</v>
       </c>
       <c r="F6" t="n">
-        <v>5.1456</v>
+        <v>5.1546</v>
       </c>
     </row>
     <row r="7">
@@ -581,7 +581,7 @@
         <v>6.2785</v>
       </c>
       <c r="F7" t="n">
-        <v>5.9456</v>
+        <v>5.9476</v>
       </c>
     </row>
     <row r="8">
@@ -603,7 +603,7 @@
         <v>4307.540039</v>
       </c>
       <c r="F8" t="n">
-        <v>7585.890137</v>
+        <v>7600.680176</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         <v>14448.580078</v>
       </c>
       <c r="F9" t="n">
-        <v>26026.601562</v>
+        <v>26133.207031</v>
       </c>
     </row>
     <row r="10">
@@ -647,7 +647,7 @@
         <v>33843.921875</v>
       </c>
       <c r="F10" t="n">
-        <v>51923.578125</v>
+        <v>51940.390625</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>1757</v>
       </c>
       <c r="F11" t="n">
-        <v>4329.299805</v>
+        <v>4376.899902</v>
       </c>
     </row>
     <row r="12">
@@ -691,7 +691,7 @@
         <v>75.029999</v>
       </c>
       <c r="F12" t="n">
-        <v>103.730003</v>
+        <v>103.169998</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>78.519997</v>
       </c>
       <c r="F13" t="n">
-        <v>102.610001</v>
+        <v>106.949997</v>
       </c>
     </row>
     <row r="14">
@@ -735,7 +735,7 @@
         <v>1256</v>
       </c>
       <c r="F14" t="n">
-        <v>1306.5</v>
+        <v>1320.25</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +757,7 @@
         <v>536.75</v>
       </c>
       <c r="F15" t="n">
-        <v>531.25</v>
+        <v>535</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -471,7 +471,7 @@
         <v>110979</v>
       </c>
       <c r="F2" t="n">
-        <v>185399.484375</v>
+        <v>184544.75</v>
       </c>
     </row>
     <row r="3">
@@ -493,7 +493,7 @@
         <v>106.489998</v>
       </c>
       <c r="F3" t="n">
-        <v>182.539993</v>
+        <v>181.610001</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>127.400002</v>
       </c>
       <c r="F4" t="n">
-        <v>109.540001</v>
+        <v>109.209999</v>
       </c>
     </row>
     <row r="5">
@@ -537,7 +537,7 @@
         <v>255</v>
       </c>
       <c r="F5" t="n">
-        <v>442.51001</v>
+        <v>444.839996</v>
       </c>
     </row>
     <row r="6">
@@ -559,7 +559,7 @@
         <v>5.4143</v>
       </c>
       <c r="F6" t="n">
-        <v>5.1546</v>
+        <v>5.1599</v>
       </c>
     </row>
     <row r="7">
@@ -581,7 +581,7 @@
         <v>6.2785</v>
       </c>
       <c r="F7" t="n">
-        <v>5.9476</v>
+        <v>5.9317</v>
       </c>
     </row>
     <row r="8">
@@ -603,7 +603,7 @@
         <v>4307.540039</v>
       </c>
       <c r="F8" t="n">
-        <v>7600.680176</v>
+        <v>7630.069824</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         <v>14448.580078</v>
       </c>
       <c r="F9" t="n">
-        <v>26133.207031</v>
+        <v>26407.919922</v>
       </c>
     </row>
     <row r="10">
@@ -647,7 +647,7 @@
         <v>33843.921875</v>
       </c>
       <c r="F10" t="n">
-        <v>51940.390625</v>
+        <v>51741.929688</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>1757</v>
       </c>
       <c r="F11" t="n">
-        <v>4376.899902</v>
+        <v>4410.5</v>
       </c>
     </row>
     <row r="12">
@@ -691,7 +691,7 @@
         <v>75.029999</v>
       </c>
       <c r="F12" t="n">
-        <v>103.169998</v>
+        <v>100.389999</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>78.519997</v>
       </c>
       <c r="F13" t="n">
-        <v>106.949997</v>
+        <v>102.959999</v>
       </c>
     </row>
     <row r="14">
@@ -735,7 +735,7 @@
         <v>1256</v>
       </c>
       <c r="F14" t="n">
-        <v>1320.25</v>
+        <v>1312.5</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +757,7 @@
         <v>536.75</v>
       </c>
       <c r="F15" t="n">
-        <v>535</v>
+        <v>528</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -471,7 +471,7 @@
         <v>110979</v>
       </c>
       <c r="F2" t="n">
-        <v>184544.75</v>
+        <v>184955.578125</v>
       </c>
     </row>
     <row r="3">
@@ -493,7 +493,7 @@
         <v>106.489998</v>
       </c>
       <c r="F3" t="n">
-        <v>181.610001</v>
+        <v>182.089996</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>127.400002</v>
       </c>
       <c r="F4" t="n">
-        <v>109.209999</v>
+        <v>108.889999</v>
       </c>
     </row>
     <row r="5">
@@ -537,7 +537,7 @@
         <v>255</v>
       </c>
       <c r="F5" t="n">
-        <v>444.839996</v>
+        <v>444.149994</v>
       </c>
     </row>
     <row r="6">
@@ -559,7 +559,7 @@
         <v>5.4143</v>
       </c>
       <c r="F6" t="n">
-        <v>5.1599</v>
+        <v>5.1563</v>
       </c>
     </row>
     <row r="7">
@@ -581,7 +581,7 @@
         <v>6.2785</v>
       </c>
       <c r="F7" t="n">
-        <v>5.9317</v>
+        <v>5.9081</v>
       </c>
     </row>
     <row r="8">
@@ -603,7 +603,7 @@
         <v>4307.540039</v>
       </c>
       <c r="F8" t="n">
-        <v>7630.069824</v>
+        <v>7623.669922</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         <v>14448.580078</v>
       </c>
       <c r="F9" t="n">
-        <v>26407.919922</v>
+        <v>26423.677734</v>
       </c>
     </row>
     <row r="10">
@@ -647,7 +647,7 @@
         <v>33843.921875</v>
       </c>
       <c r="F10" t="n">
-        <v>51741.929688</v>
+        <v>51562.378906</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>1757</v>
       </c>
       <c r="F11" t="n">
-        <v>4410.5</v>
+        <v>4391</v>
       </c>
     </row>
     <row r="12">
@@ -691,7 +691,7 @@
         <v>75.029999</v>
       </c>
       <c r="F12" t="n">
-        <v>100.389999</v>
+        <v>97.860001</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>78.519997</v>
       </c>
       <c r="F13" t="n">
-        <v>102.959999</v>
+        <v>100.040001</v>
       </c>
     </row>
     <row r="14">
@@ -722,21 +722,13 @@
           <t>soja</t>
         </is>
       </c>
-      <c r="B14" s="1" t="n">
-        <v>44469</v>
-      </c>
-      <c r="C14" s="1" t="n">
-        <v>46295</v>
-      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>61</v>
-      </c>
-      <c r="E14" t="n">
-        <v>1256</v>
-      </c>
-      <c r="F14" t="n">
-        <v>1312.5</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -757,7 +749,7 @@
         <v>536.75</v>
       </c>
       <c r="F15" t="n">
-        <v>528</v>
+        <v>526.75</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -471,7 +471,7 @@
         <v>110979</v>
       </c>
       <c r="F2" t="n">
-        <v>184955.578125</v>
+        <v>185229</v>
       </c>
     </row>
     <row r="3">
@@ -493,7 +493,7 @@
         <v>106.489998</v>
       </c>
       <c r="F3" t="n">
-        <v>182.089996</v>
+        <v>183.279999</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>127.400002</v>
       </c>
       <c r="F4" t="n">
-        <v>108.889999</v>
+        <v>109.690002</v>
       </c>
     </row>
     <row r="5">
@@ -537,7 +537,7 @@
         <v>255</v>
       </c>
       <c r="F5" t="n">
-        <v>444.149994</v>
+        <v>442.600006</v>
       </c>
     </row>
     <row r="6">
@@ -559,7 +559,7 @@
         <v>5.4143</v>
       </c>
       <c r="F6" t="n">
-        <v>5.1563</v>
+        <v>5.1421</v>
       </c>
     </row>
     <row r="7">
@@ -581,7 +581,7 @@
         <v>6.2785</v>
       </c>
       <c r="F7" t="n">
-        <v>5.9081</v>
+        <v>5.9057</v>
       </c>
     </row>
     <row r="8">
@@ -603,7 +603,7 @@
         <v>4307.540039</v>
       </c>
       <c r="F8" t="n">
-        <v>7623.669922</v>
+        <v>7650.5</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         <v>14448.580078</v>
       </c>
       <c r="F9" t="n">
-        <v>26423.677734</v>
+        <v>26522.539062</v>
       </c>
     </row>
     <row r="10">
@@ -647,7 +647,7 @@
         <v>33843.921875</v>
       </c>
       <c r="F10" t="n">
-        <v>51562.378906</v>
+        <v>51682.640625</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>1757</v>
       </c>
       <c r="F11" t="n">
-        <v>4391</v>
+        <v>4424.899902</v>
       </c>
     </row>
     <row r="12">
@@ -691,7 +691,7 @@
         <v>75.029999</v>
       </c>
       <c r="F12" t="n">
-        <v>97.860001</v>
+        <v>100.300003</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>78.519997</v>
       </c>
       <c r="F13" t="n">
-        <v>100.040001</v>
+        <v>103.870003</v>
       </c>
     </row>
     <row r="14">
@@ -722,13 +722,21 @@
           <t>soja</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
+      <c r="B14" s="1" t="n">
+        <v>44469</v>
+      </c>
+      <c r="C14" s="1" t="n">
+        <v>46295</v>
+      </c>
       <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
+        <v>61</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1256</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1303.5</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -749,7 +757,7 @@
         <v>536.75</v>
       </c>
       <c r="F15" t="n">
-        <v>526.75</v>
+        <v>527.5</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -493,7 +493,7 @@
         <v>106.489998</v>
       </c>
       <c r="F3" t="n">
-        <v>183.279999</v>
+        <v>182.470001</v>
       </c>
     </row>
     <row r="4">
@@ -537,7 +537,7 @@
         <v>255</v>
       </c>
       <c r="F5" t="n">
-        <v>442.600006</v>
+        <v>443.5</v>
       </c>
     </row>
     <row r="6">
@@ -559,7 +559,7 @@
         <v>5.4143</v>
       </c>
       <c r="F6" t="n">
-        <v>5.1421</v>
+        <v>5.1442</v>
       </c>
     </row>
     <row r="7">
@@ -691,7 +691,7 @@
         <v>75.029999</v>
       </c>
       <c r="F12" t="n">
-        <v>100.300003</v>
+        <v>96.08000199999999</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>78.519997</v>
       </c>
       <c r="F13" t="n">
-        <v>103.870003</v>
+        <v>99.290001</v>
       </c>
     </row>
     <row r="14">

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -471,7 +471,7 @@
         <v>110979</v>
       </c>
       <c r="F2" t="n">
-        <v>185229</v>
+        <v>186247.09375</v>
       </c>
     </row>
     <row r="3">
@@ -493,7 +493,7 @@
         <v>106.489998</v>
       </c>
       <c r="F3" t="n">
-        <v>182.470001</v>
+        <v>183.380005</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>127.400002</v>
       </c>
       <c r="F4" t="n">
-        <v>109.690002</v>
+        <v>111.540001</v>
       </c>
     </row>
     <row r="5">
@@ -537,7 +537,7 @@
         <v>255</v>
       </c>
       <c r="F5" t="n">
-        <v>443.5</v>
+        <v>446.429993</v>
       </c>
     </row>
     <row r="6">
@@ -559,7 +559,7 @@
         <v>5.4143</v>
       </c>
       <c r="F6" t="n">
-        <v>5.1442</v>
+        <v>5.1019</v>
       </c>
     </row>
     <row r="7">
@@ -581,7 +581,7 @@
         <v>6.2785</v>
       </c>
       <c r="F7" t="n">
-        <v>5.9057</v>
+        <v>5.8593</v>
       </c>
     </row>
     <row r="8">
@@ -603,7 +603,7 @@
         <v>4307.540039</v>
       </c>
       <c r="F8" t="n">
-        <v>7650.5</v>
+        <v>7743.27002</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         <v>14448.580078</v>
       </c>
       <c r="F9" t="n">
-        <v>26522.539062</v>
+        <v>27005.107422</v>
       </c>
     </row>
     <row r="10">
@@ -647,7 +647,7 @@
         <v>33843.921875</v>
       </c>
       <c r="F10" t="n">
-        <v>51682.640625</v>
+        <v>51959.019531</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>1757</v>
       </c>
       <c r="F11" t="n">
-        <v>4424.899902</v>
+        <v>4386.200195</v>
       </c>
     </row>
     <row r="12">
@@ -691,7 +691,7 @@
         <v>75.029999</v>
       </c>
       <c r="F12" t="n">
-        <v>96.08000199999999</v>
+        <v>92.339996</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>78.519997</v>
       </c>
       <c r="F13" t="n">
-        <v>99.290001</v>
+        <v>96.199997</v>
       </c>
     </row>
     <row r="14">
@@ -735,7 +735,7 @@
         <v>1256</v>
       </c>
       <c r="F14" t="n">
-        <v>1303.5</v>
+        <v>1325.25</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +757,7 @@
         <v>536.75</v>
       </c>
       <c r="F15" t="n">
-        <v>527.5</v>
+        <v>542.5</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -471,7 +471,7 @@
         <v>110979</v>
       </c>
       <c r="F2" t="n">
-        <v>186247.09375</v>
+        <v>185986.109375</v>
       </c>
     </row>
     <row r="3">
@@ -493,7 +493,7 @@
         <v>106.489998</v>
       </c>
       <c r="F3" t="n">
-        <v>183.380005</v>
+        <v>183.190002</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>127.400002</v>
       </c>
       <c r="F4" t="n">
-        <v>111.540001</v>
+        <v>111.32</v>
       </c>
     </row>
     <row r="5">
@@ -537,7 +537,7 @@
         <v>255</v>
       </c>
       <c r="F5" t="n">
-        <v>446.429993</v>
+        <v>449.369995</v>
       </c>
     </row>
     <row r="6">
@@ -559,7 +559,7 @@
         <v>5.4143</v>
       </c>
       <c r="F6" t="n">
-        <v>5.1019</v>
+        <v>5.1202</v>
       </c>
     </row>
     <row r="7">
@@ -581,7 +581,7 @@
         <v>6.2785</v>
       </c>
       <c r="F7" t="n">
-        <v>5.8593</v>
+        <v>5.8591</v>
       </c>
     </row>
     <row r="8">
@@ -603,7 +603,7 @@
         <v>4307.540039</v>
       </c>
       <c r="F8" t="n">
-        <v>7743.27002</v>
+        <v>7770.220215</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         <v>14448.580078</v>
       </c>
       <c r="F9" t="n">
-        <v>27005.107422</v>
+        <v>27251.701172</v>
       </c>
     </row>
     <row r="10">
@@ -647,7 +647,7 @@
         <v>33843.921875</v>
       </c>
       <c r="F10" t="n">
-        <v>51959.019531</v>
+        <v>51857.640625</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>1757</v>
       </c>
       <c r="F11" t="n">
-        <v>4386.200195</v>
+        <v>4367.5</v>
       </c>
     </row>
     <row r="12">
@@ -691,7 +691,7 @@
         <v>75.029999</v>
       </c>
       <c r="F12" t="n">
-        <v>92.339996</v>
+        <v>90.910004</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>78.519997</v>
       </c>
       <c r="F13" t="n">
-        <v>96.199997</v>
+        <v>99.470001</v>
       </c>
     </row>
     <row r="14">
@@ -735,7 +735,7 @@
         <v>1256</v>
       </c>
       <c r="F14" t="n">
-        <v>1325.25</v>
+        <v>1327.25</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +757,7 @@
         <v>536.75</v>
       </c>
       <c r="F15" t="n">
-        <v>542.5</v>
+        <v>538.25</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -471,7 +471,7 @@
         <v>110979</v>
       </c>
       <c r="F2" t="n">
-        <v>185986.109375</v>
+        <v>185576.765625</v>
       </c>
     </row>
     <row r="3">
@@ -493,7 +493,7 @@
         <v>106.489998</v>
       </c>
       <c r="F3" t="n">
-        <v>183.190002</v>
+        <v>182.740005</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>127.400002</v>
       </c>
       <c r="F4" t="n">
-        <v>111.32</v>
+        <v>111.169998</v>
       </c>
     </row>
     <row r="5">
@@ -537,7 +537,7 @@
         <v>255</v>
       </c>
       <c r="F5" t="n">
-        <v>449.369995</v>
+        <v>449.450012</v>
       </c>
     </row>
     <row r="6">
@@ -559,7 +559,7 @@
         <v>5.4143</v>
       </c>
       <c r="F6" t="n">
-        <v>5.1202</v>
+        <v>5.1167</v>
       </c>
     </row>
     <row r="7">
@@ -581,7 +581,7 @@
         <v>6.2785</v>
       </c>
       <c r="F7" t="n">
-        <v>5.8591</v>
+        <v>5.858</v>
       </c>
     </row>
     <row r="8">
@@ -603,7 +603,7 @@
         <v>4307.540039</v>
       </c>
       <c r="F8" t="n">
-        <v>7770.220215</v>
+        <v>7768.72998</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         <v>14448.580078</v>
       </c>
       <c r="F9" t="n">
-        <v>27251.701172</v>
+        <v>27249.957031</v>
       </c>
     </row>
     <row r="10">
@@ -647,7 +647,7 @@
         <v>33843.921875</v>
       </c>
       <c r="F10" t="n">
-        <v>51857.640625</v>
+        <v>51828.691406</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>1757</v>
       </c>
       <c r="F11" t="n">
-        <v>4367.5</v>
+        <v>4366</v>
       </c>
     </row>
     <row r="12">
@@ -691,7 +691,7 @@
         <v>75.029999</v>
       </c>
       <c r="F12" t="n">
-        <v>90.910004</v>
+        <v>90.699997</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>78.519997</v>
       </c>
       <c r="F13" t="n">
-        <v>99.470001</v>
+        <v>99.25</v>
       </c>
     </row>
     <row r="14">
@@ -735,7 +735,7 @@
         <v>1256</v>
       </c>
       <c r="F14" t="n">
-        <v>1327.25</v>
+        <v>1327.5</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +757,7 @@
         <v>536.75</v>
       </c>
       <c r="F15" t="n">
-        <v>538.25</v>
+        <v>538</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -471,7 +471,7 @@
         <v>110979</v>
       </c>
       <c r="F2" t="n">
-        <v>185576.765625</v>
+        <v>187575.046875</v>
       </c>
     </row>
     <row r="3">
@@ -493,7 +493,7 @@
         <v>106.489998</v>
       </c>
       <c r="F3" t="n">
-        <v>182.740005</v>
+        <v>184.679993</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>127.400002</v>
       </c>
       <c r="F4" t="n">
-        <v>111.169998</v>
+        <v>111.980003</v>
       </c>
     </row>
     <row r="5">
@@ -537,7 +537,7 @@
         <v>255</v>
       </c>
       <c r="F5" t="n">
-        <v>449.450012</v>
+        <v>448.869995</v>
       </c>
     </row>
     <row r="6">
@@ -559,7 +559,7 @@
         <v>5.4143</v>
       </c>
       <c r="F6" t="n">
-        <v>5.1167</v>
+        <v>5.1471</v>
       </c>
     </row>
     <row r="7">
@@ -581,7 +581,7 @@
         <v>6.2785</v>
       </c>
       <c r="F7" t="n">
-        <v>5.858</v>
+        <v>5.8651</v>
       </c>
     </row>
     <row r="8">
@@ -603,7 +603,7 @@
         <v>4307.540039</v>
       </c>
       <c r="F8" t="n">
-        <v>7768.72998</v>
+        <v>7725.299805</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         <v>14448.580078</v>
       </c>
       <c r="F9" t="n">
-        <v>27249.957031</v>
+        <v>26969.003906</v>
       </c>
     </row>
     <row r="10">
@@ -647,7 +647,7 @@
         <v>33843.921875</v>
       </c>
       <c r="F10" t="n">
-        <v>51828.691406</v>
+        <v>51787.929688</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>1757</v>
       </c>
       <c r="F11" t="n">
-        <v>4366</v>
+        <v>4315.5</v>
       </c>
     </row>
     <row r="12">
@@ -691,7 +691,7 @@
         <v>75.029999</v>
       </c>
       <c r="F12" t="n">
-        <v>90.699997</v>
+        <v>92.099998</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>78.519997</v>
       </c>
       <c r="F13" t="n">
-        <v>99.25</v>
+        <v>97.620003</v>
       </c>
     </row>
     <row r="14">
@@ -735,7 +735,7 @@
         <v>1256</v>
       </c>
       <c r="F14" t="n">
-        <v>1327.5</v>
+        <v>1315.75</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +757,7 @@
         <v>536.75</v>
       </c>
       <c r="F15" t="n">
-        <v>538</v>
+        <v>528.75</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -471,7 +471,7 @@
         <v>110979</v>
       </c>
       <c r="F2" t="n">
-        <v>187575.046875</v>
+        <v>185430.703125</v>
       </c>
     </row>
     <row r="3">
@@ -493,7 +493,7 @@
         <v>106.489998</v>
       </c>
       <c r="F3" t="n">
-        <v>184.679993</v>
+        <v>182.5</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>127.400002</v>
       </c>
       <c r="F4" t="n">
-        <v>111.980003</v>
+        <v>110.760002</v>
       </c>
     </row>
     <row r="5">
@@ -537,7 +537,7 @@
         <v>255</v>
       </c>
       <c r="F5" t="n">
-        <v>448.869995</v>
+        <v>449.720001</v>
       </c>
     </row>
     <row r="6">
@@ -559,7 +559,7 @@
         <v>5.4143</v>
       </c>
       <c r="F6" t="n">
-        <v>5.1471</v>
+        <v>5.1764</v>
       </c>
     </row>
     <row r="7">
@@ -581,7 +581,7 @@
         <v>6.2785</v>
       </c>
       <c r="F7" t="n">
-        <v>5.8651</v>
+        <v>5.8909</v>
       </c>
     </row>
     <row r="8">
@@ -603,7 +603,7 @@
         <v>4307.540039</v>
       </c>
       <c r="F8" t="n">
-        <v>7725.299805</v>
+        <v>7687.310059</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         <v>14448.580078</v>
       </c>
       <c r="F9" t="n">
-        <v>26969.003906</v>
+        <v>26805.265625</v>
       </c>
     </row>
     <row r="10">
@@ -647,7 +647,7 @@
         <v>33843.921875</v>
       </c>
       <c r="F10" t="n">
-        <v>51787.929688</v>
+        <v>51308.679688</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>1757</v>
       </c>
       <c r="F11" t="n">
-        <v>4315.5</v>
+        <v>4298.899902</v>
       </c>
     </row>
     <row r="12">
@@ -691,7 +691,7 @@
         <v>75.029999</v>
       </c>
       <c r="F12" t="n">
-        <v>92.099998</v>
+        <v>94.66999800000001</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>78.519997</v>
       </c>
       <c r="F13" t="n">
-        <v>97.620003</v>
+        <v>100.309998</v>
       </c>
     </row>
     <row r="14">
@@ -735,7 +735,7 @@
         <v>1256</v>
       </c>
       <c r="F14" t="n">
-        <v>1315.75</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +757,7 @@
         <v>536.75</v>
       </c>
       <c r="F15" t="n">
-        <v>528.75</v>
+        <v>527.75</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -471,7 +471,7 @@
         <v>110979</v>
       </c>
       <c r="F2" t="n">
-        <v>185430.703125</v>
+        <v>185707.59375</v>
       </c>
     </row>
     <row r="3">
@@ -493,7 +493,7 @@
         <v>106.489998</v>
       </c>
       <c r="F3" t="n">
-        <v>182.5</v>
+        <v>182.770004</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>127.400002</v>
       </c>
       <c r="F4" t="n">
-        <v>110.760002</v>
+        <v>110.959999</v>
       </c>
     </row>
     <row r="5">
@@ -537,7 +537,7 @@
         <v>255</v>
       </c>
       <c r="F5" t="n">
-        <v>449.720001</v>
+        <v>449.549988</v>
       </c>
     </row>
     <row r="6">
@@ -559,7 +559,7 @@
         <v>5.4143</v>
       </c>
       <c r="F6" t="n">
-        <v>5.1764</v>
+        <v>5.1808</v>
       </c>
     </row>
     <row r="7">
@@ -581,7 +581,7 @@
         <v>6.2785</v>
       </c>
       <c r="F7" t="n">
-        <v>5.8909</v>
+        <v>5.8912</v>
       </c>
     </row>
     <row r="8">
@@ -603,7 +603,7 @@
         <v>4307.540039</v>
       </c>
       <c r="F8" t="n">
-        <v>7687.310059</v>
+        <v>7687.410156</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         <v>14448.580078</v>
       </c>
       <c r="F9" t="n">
-        <v>26805.265625</v>
+        <v>26794.8125</v>
       </c>
     </row>
     <row r="10">
@@ -647,7 +647,7 @@
         <v>33843.921875</v>
       </c>
       <c r="F10" t="n">
-        <v>51308.679688</v>
+        <v>51309.371094</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>1757</v>
       </c>
       <c r="F11" t="n">
-        <v>4298.899902</v>
+        <v>4296.299805</v>
       </c>
     </row>
     <row r="12">
@@ -691,7 +691,7 @@
         <v>75.029999</v>
       </c>
       <c r="F12" t="n">
-        <v>94.66999800000001</v>
+        <v>94.720001</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>78.519997</v>
       </c>
       <c r="F13" t="n">
-        <v>100.309998</v>
+        <v>100.32</v>
       </c>
     </row>
     <row r="14">
@@ -735,7 +735,7 @@
         <v>1256</v>
       </c>
       <c r="F14" t="n">
-        <v>1316</v>
+        <v>1317.5</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +757,7 @@
         <v>536.75</v>
       </c>
       <c r="F15" t="n">
-        <v>527.75</v>
+        <v>530</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -471,7 +471,7 @@
         <v>110979</v>
       </c>
       <c r="F2" t="n">
-        <v>185707.59375</v>
+        <v>182428.5</v>
       </c>
     </row>
     <row r="3">
@@ -493,7 +493,7 @@
         <v>106.489998</v>
       </c>
       <c r="F3" t="n">
-        <v>182.770004</v>
+        <v>179.610001</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>127.400002</v>
       </c>
       <c r="F4" t="n">
-        <v>110.959999</v>
+        <v>109.449997</v>
       </c>
     </row>
     <row r="5">
@@ -537,7 +537,7 @@
         <v>255</v>
       </c>
       <c r="F5" t="n">
-        <v>449.549988</v>
+        <v>453.279999</v>
       </c>
     </row>
     <row r="6">
@@ -559,7 +559,7 @@
         <v>5.4143</v>
       </c>
       <c r="F6" t="n">
-        <v>5.1808</v>
+        <v>5.204</v>
       </c>
     </row>
     <row r="7">
@@ -581,7 +581,7 @@
         <v>6.2785</v>
       </c>
       <c r="F7" t="n">
-        <v>5.8912</v>
+        <v>5.9357</v>
       </c>
     </row>
     <row r="8">
@@ -603,7 +603,7 @@
         <v>4307.540039</v>
       </c>
       <c r="F8" t="n">
-        <v>7687.410156</v>
+        <v>7712.609863</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         <v>14448.580078</v>
       </c>
       <c r="F9" t="n">
-        <v>26794.8125</v>
+        <v>26965.560547</v>
       </c>
     </row>
     <row r="10">
@@ -647,7 +647,7 @@
         <v>33843.921875</v>
       </c>
       <c r="F10" t="n">
-        <v>51309.371094</v>
+        <v>51492.351562</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>1757</v>
       </c>
       <c r="F11" t="n">
-        <v>4296.299805</v>
+        <v>4306.899902</v>
       </c>
     </row>
     <row r="12">
@@ -691,7 +691,7 @@
         <v>75.029999</v>
       </c>
       <c r="F12" t="n">
-        <v>94.720001</v>
+        <v>94.099998</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>78.519997</v>
       </c>
       <c r="F13" t="n">
-        <v>100.32</v>
+        <v>99.589996</v>
       </c>
     </row>
     <row r="14">
@@ -735,7 +735,7 @@
         <v>1256</v>
       </c>
       <c r="F14" t="n">
-        <v>1317.5</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +757,7 @@
         <v>536.75</v>
       </c>
       <c r="F15" t="n">
-        <v>530</v>
+        <v>521.25</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -471,7 +471,7 @@
         <v>110979</v>
       </c>
       <c r="F2" t="n">
-        <v>182428.5</v>
+        <v>183477</v>
       </c>
     </row>
     <row r="3">
@@ -493,7 +493,7 @@
         <v>106.489998</v>
       </c>
       <c r="F3" t="n">
-        <v>179.610001</v>
+        <v>180.869995</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>127.400002</v>
       </c>
       <c r="F4" t="n">
-        <v>109.449997</v>
+        <v>109.949997</v>
       </c>
     </row>
     <row r="5">
@@ -537,7 +537,7 @@
         <v>255</v>
       </c>
       <c r="F5" t="n">
-        <v>453.279999</v>
+        <v>451.149994</v>
       </c>
     </row>
     <row r="6">
@@ -559,7 +559,7 @@
         <v>5.4143</v>
       </c>
       <c r="F6" t="n">
-        <v>5.204</v>
+        <v>5.1866</v>
       </c>
     </row>
     <row r="7">
@@ -581,7 +581,7 @@
         <v>6.2785</v>
       </c>
       <c r="F7" t="n">
-        <v>5.9357</v>
+        <v>5.9081</v>
       </c>
     </row>
     <row r="8">
@@ -603,7 +603,7 @@
         <v>4307.540039</v>
       </c>
       <c r="F8" t="n">
-        <v>7712.609863</v>
+        <v>7743.410156</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         <v>14448.580078</v>
       </c>
       <c r="F9" t="n">
-        <v>26965.560547</v>
+        <v>27068.720703</v>
       </c>
     </row>
     <row r="10">
@@ -647,7 +647,7 @@
         <v>33843.921875</v>
       </c>
       <c r="F10" t="n">
-        <v>51492.351562</v>
+        <v>51828.621094</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>1757</v>
       </c>
       <c r="F11" t="n">
-        <v>4306.899902</v>
+        <v>4321.200195</v>
       </c>
     </row>
     <row r="12">
@@ -691,7 +691,7 @@
         <v>75.029999</v>
       </c>
       <c r="F12" t="n">
-        <v>94.099998</v>
+        <v>92.410004</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>78.519997</v>
       </c>
       <c r="F13" t="n">
-        <v>99.589996</v>
+        <v>104.32</v>
       </c>
     </row>
     <row r="14">
@@ -735,7 +735,7 @@
         <v>1256</v>
       </c>
       <c r="F14" t="n">
-        <v>1305</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +757,7 @@
         <v>536.75</v>
       </c>
       <c r="F15" t="n">
-        <v>521.25</v>
+        <v>528.25</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -493,7 +493,7 @@
         <v>106.489998</v>
       </c>
       <c r="F3" t="n">
-        <v>180.869995</v>
+        <v>180.820007</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>127.400002</v>
       </c>
       <c r="F4" t="n">
-        <v>109.949997</v>
+        <v>110.449997</v>
       </c>
     </row>
     <row r="5">
@@ -537,7 +537,7 @@
         <v>255</v>
       </c>
       <c r="F5" t="n">
-        <v>451.149994</v>
+        <v>453</v>
       </c>
     </row>
     <row r="6">
@@ -713,7 +713,7 @@
         <v>78.519997</v>
       </c>
       <c r="F13" t="n">
-        <v>104.32</v>
+        <v>97.44000200000001</v>
       </c>
     </row>
     <row r="14">

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -471,7 +471,7 @@
         <v>110979</v>
       </c>
       <c r="F2" t="n">
-        <v>183477</v>
+        <v>183439.546875</v>
       </c>
     </row>
     <row r="3">
@@ -493,7 +493,7 @@
         <v>106.489998</v>
       </c>
       <c r="F3" t="n">
-        <v>180.820007</v>
+        <v>180.580002</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>127.400002</v>
       </c>
       <c r="F4" t="n">
-        <v>110.449997</v>
+        <v>109.720001</v>
       </c>
     </row>
     <row r="5">
@@ -537,7 +537,7 @@
         <v>255</v>
       </c>
       <c r="F5" t="n">
-        <v>453</v>
+        <v>453.25</v>
       </c>
     </row>
     <row r="6">
@@ -559,7 +559,7 @@
         <v>5.4143</v>
       </c>
       <c r="F6" t="n">
-        <v>5.1866</v>
+        <v>5.2176</v>
       </c>
     </row>
     <row r="7">
@@ -581,7 +581,7 @@
         <v>6.2785</v>
       </c>
       <c r="F7" t="n">
-        <v>5.9081</v>
+        <v>5.9337</v>
       </c>
     </row>
     <row r="8">
@@ -603,7 +603,7 @@
         <v>4307.540039</v>
       </c>
       <c r="F8" t="n">
-        <v>7743.410156</v>
+        <v>7702.799805</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         <v>14448.580078</v>
       </c>
       <c r="F9" t="n">
-        <v>27068.720703</v>
+        <v>26903.330078</v>
       </c>
     </row>
     <row r="10">
@@ -647,7 +647,7 @@
         <v>33843.921875</v>
       </c>
       <c r="F10" t="n">
-        <v>51828.621094</v>
+        <v>51612.378906</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>1757</v>
       </c>
       <c r="F11" t="n">
-        <v>4321.200195</v>
+        <v>4170.799805</v>
       </c>
     </row>
     <row r="12">
@@ -691,7 +691,7 @@
         <v>75.029999</v>
       </c>
       <c r="F12" t="n">
-        <v>92.410004</v>
+        <v>92.589996</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>78.519997</v>
       </c>
       <c r="F13" t="n">
-        <v>97.44000200000001</v>
+        <v>97.69000200000001</v>
       </c>
     </row>
     <row r="14">
@@ -735,7 +735,7 @@
         <v>1256</v>
       </c>
       <c r="F14" t="n">
-        <v>1319</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +757,7 @@
         <v>536.75</v>
       </c>
       <c r="F15" t="n">
-        <v>528.25</v>
+        <v>522</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -471,7 +471,7 @@
         <v>110979</v>
       </c>
       <c r="F2" t="n">
-        <v>183439.546875</v>
+        <v>183466.265625</v>
       </c>
     </row>
     <row r="3">
@@ -493,7 +493,7 @@
         <v>106.489998</v>
       </c>
       <c r="F3" t="n">
-        <v>180.580002</v>
+        <v>180.649994</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>127.400002</v>
       </c>
       <c r="F4" t="n">
-        <v>109.720001</v>
+        <v>109.889999</v>
       </c>
     </row>
     <row r="5">
@@ -537,7 +537,7 @@
         <v>255</v>
       </c>
       <c r="F5" t="n">
-        <v>453.25</v>
+        <v>452.769989</v>
       </c>
     </row>
     <row r="6">
@@ -559,7 +559,7 @@
         <v>5.4143</v>
       </c>
       <c r="F6" t="n">
-        <v>5.2176</v>
+        <v>5.2163</v>
       </c>
     </row>
     <row r="7">
@@ -581,7 +581,7 @@
         <v>6.2785</v>
       </c>
       <c r="F7" t="n">
-        <v>5.9337</v>
+        <v>5.9327</v>
       </c>
     </row>
     <row r="8">
@@ -603,7 +603,7 @@
         <v>4307.540039</v>
       </c>
       <c r="F8" t="n">
-        <v>7702.799805</v>
+        <v>7702.350098</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         <v>14448.580078</v>
       </c>
       <c r="F9" t="n">
-        <v>26903.330078</v>
+        <v>26899.5</v>
       </c>
     </row>
     <row r="10">
@@ -647,7 +647,7 @@
         <v>33843.921875</v>
       </c>
       <c r="F10" t="n">
-        <v>51612.378906</v>
+        <v>51614.789062</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>1757</v>
       </c>
       <c r="F11" t="n">
-        <v>4170.799805</v>
+        <v>4170.399902</v>
       </c>
     </row>
     <row r="12">
@@ -691,7 +691,7 @@
         <v>75.029999</v>
       </c>
       <c r="F12" t="n">
-        <v>92.589996</v>
+        <v>92.55999799999999</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>78.519997</v>
       </c>
       <c r="F13" t="n">
-        <v>97.69000200000001</v>
+        <v>97.769997</v>
       </c>
     </row>
     <row r="14">
@@ -735,7 +735,7 @@
         <v>1256</v>
       </c>
       <c r="F14" t="n">
-        <v>1287</v>
+        <v>1288.25</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +757,7 @@
         <v>536.75</v>
       </c>
       <c r="F15" t="n">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -471,7 +471,7 @@
         <v>110979</v>
       </c>
       <c r="F2" t="n">
-        <v>183466.265625</v>
+        <v>182477.703125</v>
       </c>
     </row>
     <row r="3">
@@ -493,7 +493,7 @@
         <v>106.489998</v>
       </c>
       <c r="F3" t="n">
-        <v>180.649994</v>
+        <v>179.699997</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>127.400002</v>
       </c>
       <c r="F4" t="n">
-        <v>109.889999</v>
+        <v>108.629997</v>
       </c>
     </row>
     <row r="5">
@@ -537,7 +537,7 @@
         <v>255</v>
       </c>
       <c r="F5" t="n">
-        <v>452.769989</v>
+        <v>452.440002</v>
       </c>
     </row>
     <row r="6">
@@ -559,7 +559,7 @@
         <v>5.4143</v>
       </c>
       <c r="F6" t="n">
-        <v>5.2163</v>
+        <v>5.2304</v>
       </c>
     </row>
     <row r="7">
@@ -581,7 +581,7 @@
         <v>6.2785</v>
       </c>
       <c r="F7" t="n">
-        <v>5.9327</v>
+        <v>5.9299</v>
       </c>
     </row>
     <row r="8">
@@ -603,7 +603,7 @@
         <v>4307.540039</v>
       </c>
       <c r="F8" t="n">
-        <v>7702.350098</v>
+        <v>7660.640137</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         <v>14448.580078</v>
       </c>
       <c r="F9" t="n">
-        <v>26899.5</v>
+        <v>26774.152344</v>
       </c>
     </row>
     <row r="10">
@@ -647,7 +647,7 @@
         <v>33843.921875</v>
       </c>
       <c r="F10" t="n">
-        <v>51614.789062</v>
+        <v>51159.171875</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>1757</v>
       </c>
       <c r="F11" t="n">
-        <v>4170.399902</v>
+        <v>4183.600098</v>
       </c>
     </row>
     <row r="12">
@@ -691,7 +691,7 @@
         <v>75.029999</v>
       </c>
       <c r="F12" t="n">
-        <v>92.55999799999999</v>
+        <v>90.720001</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>78.519997</v>
       </c>
       <c r="F13" t="n">
-        <v>97.769997</v>
+        <v>96.80999799999999</v>
       </c>
     </row>
     <row r="14">
@@ -735,7 +735,7 @@
         <v>1256</v>
       </c>
       <c r="F14" t="n">
-        <v>1288.25</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +757,7 @@
         <v>536.75</v>
       </c>
       <c r="F15" t="n">
-        <v>523</v>
+        <v>521.25</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -471,7 +471,7 @@
         <v>110979</v>
       </c>
       <c r="F2" t="n">
-        <v>182477.703125</v>
+        <v>182503.359375</v>
       </c>
     </row>
     <row r="3">
@@ -493,7 +493,7 @@
         <v>106.489998</v>
       </c>
       <c r="F3" t="n">
-        <v>179.699997</v>
+        <v>179.679993</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>127.400002</v>
       </c>
       <c r="F4" t="n">
-        <v>108.629997</v>
+        <v>108.690002</v>
       </c>
     </row>
     <row r="5">
@@ -537,7 +537,7 @@
         <v>255</v>
       </c>
       <c r="F5" t="n">
-        <v>452.440002</v>
+        <v>452.390015</v>
       </c>
     </row>
     <row r="6">
@@ -559,7 +559,7 @@
         <v>5.4143</v>
       </c>
       <c r="F6" t="n">
-        <v>5.2304</v>
+        <v>5.2357</v>
       </c>
     </row>
     <row r="7">
@@ -581,7 +581,7 @@
         <v>6.2785</v>
       </c>
       <c r="F7" t="n">
-        <v>5.9299</v>
+        <v>5.9313</v>
       </c>
     </row>
     <row r="8">
@@ -603,7 +603,7 @@
         <v>4307.540039</v>
       </c>
       <c r="F8" t="n">
-        <v>7660.640137</v>
+        <v>7660.899902</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         <v>14448.580078</v>
       </c>
       <c r="F9" t="n">
-        <v>26774.152344</v>
+        <v>26779.210938</v>
       </c>
     </row>
     <row r="10">
@@ -647,7 +647,7 @@
         <v>33843.921875</v>
       </c>
       <c r="F10" t="n">
-        <v>51159.171875</v>
+        <v>51162.320312</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>1757</v>
       </c>
       <c r="F11" t="n">
-        <v>4183.600098</v>
+        <v>4185.399902</v>
       </c>
     </row>
     <row r="12">
@@ -691,7 +691,7 @@
         <v>75.029999</v>
       </c>
       <c r="F12" t="n">
-        <v>90.720001</v>
+        <v>90.44000200000001</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>78.519997</v>
       </c>
       <c r="F13" t="n">
-        <v>96.80999799999999</v>
+        <v>96.769997</v>
       </c>
     </row>
     <row r="14">
@@ -735,7 +735,7 @@
         <v>1256</v>
       </c>
       <c r="F14" t="n">
-        <v>1297</v>
+        <v>1298.75</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +757,7 @@
         <v>536.75</v>
       </c>
       <c r="F15" t="n">
-        <v>521.25</v>
+        <v>522</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -471,7 +471,7 @@
         <v>110979</v>
       </c>
       <c r="F2" t="n">
-        <v>182503.359375</v>
+        <v>185742.0625</v>
       </c>
     </row>
     <row r="3">
@@ -493,7 +493,7 @@
         <v>106.489998</v>
       </c>
       <c r="F3" t="n">
-        <v>179.679993</v>
+        <v>182.880005</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>127.400002</v>
       </c>
       <c r="F4" t="n">
-        <v>108.690002</v>
+        <v>110.900002</v>
       </c>
     </row>
     <row r="5">
@@ -537,7 +537,7 @@
         <v>255</v>
       </c>
       <c r="F5" t="n">
-        <v>452.390015</v>
+        <v>450.890015</v>
       </c>
     </row>
     <row r="6">
@@ -559,7 +559,7 @@
         <v>5.4143</v>
       </c>
       <c r="F6" t="n">
-        <v>5.2357</v>
+        <v>5.1848</v>
       </c>
     </row>
     <row r="7">
@@ -581,7 +581,7 @@
         <v>6.2785</v>
       </c>
       <c r="F7" t="n">
-        <v>5.9313</v>
+        <v>5.8759</v>
       </c>
     </row>
     <row r="8">
@@ -603,7 +603,7 @@
         <v>4307.540039</v>
       </c>
       <c r="F8" t="n">
-        <v>7660.899902</v>
+        <v>7715.97998</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         <v>14448.580078</v>
       </c>
       <c r="F9" t="n">
-        <v>26779.210938</v>
+        <v>27077.017578</v>
       </c>
     </row>
     <row r="10">
@@ -647,7 +647,7 @@
         <v>33843.921875</v>
       </c>
       <c r="F10" t="n">
-        <v>51162.320312</v>
+        <v>51323.691406</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>1757</v>
       </c>
       <c r="F11" t="n">
-        <v>4185.399902</v>
+        <v>4191.299805</v>
       </c>
     </row>
     <row r="12">
@@ -691,7 +691,7 @@
         <v>75.029999</v>
       </c>
       <c r="F12" t="n">
-        <v>90.44000200000001</v>
+        <v>91.379997</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>78.519997</v>
       </c>
       <c r="F13" t="n">
-        <v>96.769997</v>
+        <v>98.83000199999999</v>
       </c>
     </row>
     <row r="14">
@@ -735,7 +735,7 @@
         <v>1256</v>
       </c>
       <c r="F14" t="n">
-        <v>1298.75</v>
+        <v>1309.75</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +757,7 @@
         <v>536.75</v>
       </c>
       <c r="F15" t="n">
-        <v>522</v>
+        <v>513.5</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -471,7 +471,7 @@
         <v>110979</v>
       </c>
       <c r="F2" t="n">
-        <v>185742.0625</v>
+        <v>185892.640625</v>
       </c>
     </row>
     <row r="3">
@@ -493,7 +493,7 @@
         <v>106.489998</v>
       </c>
       <c r="F3" t="n">
-        <v>182.880005</v>
+        <v>183.020004</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>127.400002</v>
       </c>
       <c r="F4" t="n">
-        <v>110.900002</v>
+        <v>110.860001</v>
       </c>
     </row>
     <row r="5">
@@ -537,7 +537,7 @@
         <v>255</v>
       </c>
       <c r="F5" t="n">
-        <v>450.890015</v>
+        <v>451.519989</v>
       </c>
     </row>
     <row r="6">
@@ -559,7 +559,7 @@
         <v>5.4143</v>
       </c>
       <c r="F6" t="n">
-        <v>5.1848</v>
+        <v>5.1838</v>
       </c>
     </row>
     <row r="7">
@@ -581,7 +581,7 @@
         <v>6.2785</v>
       </c>
       <c r="F7" t="n">
-        <v>5.8759</v>
+        <v>5.8751</v>
       </c>
     </row>
     <row r="8">
@@ -603,7 +603,7 @@
         <v>4307.540039</v>
       </c>
       <c r="F8" t="n">
-        <v>7715.97998</v>
+        <v>7711.649902</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         <v>14448.580078</v>
       </c>
       <c r="F9" t="n">
-        <v>27077.017578</v>
+        <v>27062.792969</v>
       </c>
     </row>
     <row r="10">
@@ -647,7 +647,7 @@
         <v>33843.921875</v>
       </c>
       <c r="F10" t="n">
-        <v>51323.691406</v>
+        <v>51319.070312</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>1757</v>
       </c>
       <c r="F11" t="n">
-        <v>4191.299805</v>
+        <v>4189.299805</v>
       </c>
     </row>
     <row r="12">
@@ -735,7 +735,7 @@
         <v>1256</v>
       </c>
       <c r="F14" t="n">
-        <v>1309.75</v>
+        <v>1306.5</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +757,7 @@
         <v>536.75</v>
       </c>
       <c r="F15" t="n">
-        <v>513.5</v>
+        <v>507.5</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -459,19 +459,19 @@
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="D2" t="n">
         <v>61</v>
       </c>
       <c r="E2" t="n">
-        <v>110979</v>
+        <v>103501</v>
       </c>
       <c r="F2" t="n">
-        <v>185892.640625</v>
+        <v>186810.84375</v>
       </c>
     </row>
     <row r="3">
@@ -481,19 +481,19 @@
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="D3" t="n">
         <v>61</v>
       </c>
       <c r="E3" t="n">
-        <v>106.489998</v>
+        <v>99.68000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>183.020004</v>
+        <v>183.960007</v>
       </c>
     </row>
     <row r="4">
@@ -503,19 +503,19 @@
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="D4" t="n">
         <v>61</v>
       </c>
       <c r="E4" t="n">
-        <v>127.400002</v>
+        <v>111.199997</v>
       </c>
       <c r="F4" t="n">
-        <v>110.860001</v>
+        <v>112.709999</v>
       </c>
     </row>
     <row r="5">
@@ -525,19 +525,19 @@
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="D5" t="n">
         <v>61</v>
       </c>
       <c r="E5" t="n">
-        <v>255</v>
+        <v>283</v>
       </c>
       <c r="F5" t="n">
-        <v>451.519989</v>
+        <v>451.859985</v>
       </c>
     </row>
     <row r="6">
@@ -547,19 +547,19 @@
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="D6" t="n">
         <v>61</v>
       </c>
       <c r="E6" t="n">
-        <v>5.4143</v>
+        <v>5.6449</v>
       </c>
       <c r="F6" t="n">
-        <v>5.1838</v>
+        <v>5.2282</v>
       </c>
     </row>
     <row r="7">
@@ -569,19 +569,19 @@
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="D7" t="n">
         <v>61</v>
       </c>
       <c r="E7" t="n">
-        <v>6.2785</v>
+        <v>6.593</v>
       </c>
       <c r="F7" t="n">
-        <v>5.8751</v>
+        <v>5.8715</v>
       </c>
     </row>
     <row r="8">
@@ -591,19 +591,19 @@
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="D8" t="n">
         <v>61</v>
       </c>
       <c r="E8" t="n">
-        <v>4307.540039</v>
+        <v>4605.379883</v>
       </c>
       <c r="F8" t="n">
-        <v>7711.649902</v>
+        <v>7647.740234</v>
       </c>
     </row>
     <row r="9">
@@ -613,19 +613,19 @@
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="D9" t="n">
         <v>61</v>
       </c>
       <c r="E9" t="n">
-        <v>14448.580078</v>
+        <v>15498.389648</v>
       </c>
       <c r="F9" t="n">
-        <v>27062.792969</v>
+        <v>26818.607422</v>
       </c>
     </row>
     <row r="10">
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="D10" t="n">
         <v>61</v>
       </c>
       <c r="E10" t="n">
-        <v>33843.921875</v>
+        <v>35819.558594</v>
       </c>
       <c r="F10" t="n">
-        <v>51319.070312</v>
+        <v>50836.351562</v>
       </c>
     </row>
     <row r="11">
@@ -657,19 +657,19 @@
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="D11" t="n">
         <v>61</v>
       </c>
       <c r="E11" t="n">
-        <v>1757</v>
+        <v>1783.900024</v>
       </c>
       <c r="F11" t="n">
-        <v>4189.299805</v>
+        <v>4195.399902</v>
       </c>
     </row>
     <row r="12">
@@ -679,19 +679,19 @@
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="D12" t="n">
         <v>61</v>
       </c>
       <c r="E12" t="n">
-        <v>75.029999</v>
+        <v>83.56999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>91.379997</v>
+        <v>91.910004</v>
       </c>
     </row>
     <row r="13">
@@ -701,19 +701,19 @@
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="D13" t="n">
         <v>61</v>
       </c>
       <c r="E13" t="n">
-        <v>78.519997</v>
+        <v>84.379997</v>
       </c>
       <c r="F13" t="n">
-        <v>98.83000199999999</v>
+        <v>101.080002</v>
       </c>
     </row>
     <row r="14">
@@ -723,19 +723,19 @@
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="D14" t="n">
         <v>61</v>
       </c>
       <c r="E14" t="n">
-        <v>1256</v>
+        <v>1235.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1306.5</v>
+        <v>1277.25</v>
       </c>
     </row>
     <row r="15">
@@ -745,19 +745,19 @@
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="D15" t="n">
         <v>61</v>
       </c>
       <c r="E15" t="n">
-        <v>536.75</v>
+        <v>568.25</v>
       </c>
       <c r="F15" t="n">
-        <v>507.5</v>
+        <v>497.75</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -471,7 +471,7 @@
         <v>103501</v>
       </c>
       <c r="F2" t="n">
-        <v>186810.84375</v>
+        <v>186864.640625</v>
       </c>
     </row>
     <row r="3">
@@ -493,7 +493,7 @@
         <v>99.68000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>183.960007</v>
+        <v>184.139999</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>111.199997</v>
       </c>
       <c r="F4" t="n">
-        <v>112.709999</v>
+        <v>113.480003</v>
       </c>
     </row>
     <row r="5">
@@ -537,7 +537,7 @@
         <v>283</v>
       </c>
       <c r="F5" t="n">
-        <v>451.859985</v>
+        <v>454.899994</v>
       </c>
     </row>
     <row r="6">
@@ -559,7 +559,7 @@
         <v>5.6449</v>
       </c>
       <c r="F6" t="n">
-        <v>5.2282</v>
+        <v>5.225</v>
       </c>
     </row>
     <row r="7">
@@ -581,7 +581,7 @@
         <v>6.593</v>
       </c>
       <c r="F7" t="n">
-        <v>5.8715</v>
+        <v>5.8793</v>
       </c>
     </row>
     <row r="8">
@@ -603,7 +603,7 @@
         <v>4605.379883</v>
       </c>
       <c r="F8" t="n">
-        <v>7647.740234</v>
+        <v>7723.790039</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         <v>15498.389648</v>
       </c>
       <c r="F9" t="n">
-        <v>26818.607422</v>
+        <v>27210.888672</v>
       </c>
     </row>
     <row r="10">
@@ -647,7 +647,7 @@
         <v>35819.558594</v>
       </c>
       <c r="F10" t="n">
-        <v>50836.351562</v>
+        <v>51103.199219</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>1783.900024</v>
       </c>
       <c r="F11" t="n">
-        <v>4195.399902</v>
+        <v>4160.399902</v>
       </c>
     </row>
     <row r="12">
@@ -691,7 +691,7 @@
         <v>83.56999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>91.910004</v>
+        <v>90.81999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>84.379997</v>
       </c>
       <c r="F13" t="n">
-        <v>101.080002</v>
+        <v>101.379997</v>
       </c>
     </row>
     <row r="14">
@@ -735,7 +735,7 @@
         <v>1235.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1277.25</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +757,7 @@
         <v>568.25</v>
       </c>
       <c r="F15" t="n">
-        <v>497.75</v>
+        <v>496.25</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -471,7 +471,7 @@
         <v>103501</v>
       </c>
       <c r="F2" t="n">
-        <v>186864.640625</v>
+        <v>187130.234375</v>
       </c>
     </row>
     <row r="3">
@@ -493,7 +493,7 @@
         <v>99.68000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>184.139999</v>
+        <v>184.320007</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>111.199997</v>
       </c>
       <c r="F4" t="n">
-        <v>113.480003</v>
+        <v>113.379997</v>
       </c>
     </row>
     <row r="5">
@@ -537,7 +537,7 @@
         <v>283</v>
       </c>
       <c r="F5" t="n">
-        <v>454.899994</v>
+        <v>454.670013</v>
       </c>
     </row>
     <row r="6">
@@ -559,7 +559,7 @@
         <v>5.6449</v>
       </c>
       <c r="F6" t="n">
-        <v>5.225</v>
+        <v>5.2234</v>
       </c>
     </row>
     <row r="7">
@@ -581,7 +581,7 @@
         <v>6.593</v>
       </c>
       <c r="F7" t="n">
-        <v>5.8793</v>
+        <v>5.8805</v>
       </c>
     </row>
     <row r="8">
@@ -603,7 +603,7 @@
         <v>4605.379883</v>
       </c>
       <c r="F8" t="n">
-        <v>7723.790039</v>
+        <v>7725.560059</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         <v>15498.389648</v>
       </c>
       <c r="F9" t="n">
-        <v>27210.888672</v>
+        <v>27222.126953</v>
       </c>
     </row>
     <row r="10">
@@ -647,7 +647,7 @@
         <v>35819.558594</v>
       </c>
       <c r="F10" t="n">
-        <v>51103.199219</v>
+        <v>51112.210938</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>1783.900024</v>
       </c>
       <c r="F11" t="n">
-        <v>4160.399902</v>
+        <v>4155.200195</v>
       </c>
     </row>
     <row r="12">
@@ -691,7 +691,7 @@
         <v>83.56999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>90.81999999999999</v>
+        <v>90.970001</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>84.379997</v>
       </c>
       <c r="F13" t="n">
-        <v>101.379997</v>
+        <v>101.400002</v>
       </c>
     </row>
     <row r="14">
@@ -735,7 +735,7 @@
         <v>1235.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1279</v>
+        <v>1279.25</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +757,7 @@
         <v>568.25</v>
       </c>
       <c r="F15" t="n">
-        <v>496.25</v>
+        <v>496.75</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -471,7 +471,7 @@
         <v>103501</v>
       </c>
       <c r="F2" t="n">
-        <v>187130.234375</v>
+        <v>192115</v>
       </c>
     </row>
     <row r="3">
@@ -493,7 +493,7 @@
         <v>99.68000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>184.320007</v>
+        <v>184.410004</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>111.199997</v>
       </c>
       <c r="F4" t="n">
-        <v>113.379997</v>
+        <v>113.019997</v>
       </c>
     </row>
     <row r="5">
@@ -537,7 +537,7 @@
         <v>283</v>
       </c>
       <c r="F5" t="n">
-        <v>454.670013</v>
+        <v>452.079987</v>
       </c>
     </row>
     <row r="6">
@@ -559,7 +559,7 @@
         <v>5.6449</v>
       </c>
       <c r="F6" t="n">
-        <v>5.2234</v>
+        <v>5.2223</v>
       </c>
     </row>
     <row r="7">
@@ -581,7 +581,7 @@
         <v>6.593</v>
       </c>
       <c r="F7" t="n">
-        <v>5.8805</v>
+        <v>5.8702</v>
       </c>
     </row>
     <row r="8">
@@ -603,7 +603,7 @@
         <v>4605.379883</v>
       </c>
       <c r="F8" t="n">
-        <v>7725.560059</v>
+        <v>7722.720215</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         <v>15498.389648</v>
       </c>
       <c r="F9" t="n">
-        <v>27222.126953</v>
+        <v>27190.859375</v>
       </c>
     </row>
     <row r="10">
@@ -647,7 +647,7 @@
         <v>35819.558594</v>
       </c>
       <c r="F10" t="n">
-        <v>51112.210938</v>
+        <v>51176.960938</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>1783.900024</v>
       </c>
       <c r="F11" t="n">
-        <v>4155.200195</v>
+        <v>4162.299805</v>
       </c>
     </row>
     <row r="12">
@@ -691,7 +691,7 @@
         <v>83.56999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>90.970001</v>
+        <v>91.110001</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>84.379997</v>
       </c>
       <c r="F13" t="n">
-        <v>101.400002</v>
+        <v>102.25</v>
       </c>
     </row>
     <row r="14">
@@ -735,7 +735,7 @@
         <v>1235.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1279.25</v>
+        <v>1278.25</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +757,7 @@
         <v>568.25</v>
       </c>
       <c r="F15" t="n">
-        <v>496.75</v>
+        <v>497.75</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -493,7 +493,7 @@
         <v>99.68000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>184.410004</v>
+        <v>190</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>111.199997</v>
       </c>
       <c r="F4" t="n">
-        <v>113.019997</v>
+        <v>116.339996</v>
       </c>
     </row>
     <row r="5">
@@ -537,7 +537,7 @@
         <v>283</v>
       </c>
       <c r="F5" t="n">
-        <v>452.079987</v>
+        <v>454.700012</v>
       </c>
     </row>
     <row r="6">

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -471,7 +471,7 @@
         <v>103501</v>
       </c>
       <c r="F2" t="n">
-        <v>192115</v>
+        <v>208982.96875</v>
       </c>
     </row>
     <row r="3">
@@ -493,7 +493,7 @@
         <v>99.68000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>190</v>
+        <v>205.960007</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>111.199997</v>
       </c>
       <c r="F4" t="n">
-        <v>116.339996</v>
+        <v>128.25</v>
       </c>
     </row>
     <row r="5">
@@ -537,7 +537,7 @@
         <v>283</v>
       </c>
       <c r="F5" t="n">
-        <v>454.700012</v>
+        <v>439.059998</v>
       </c>
     </row>
     <row r="6">
@@ -559,7 +559,7 @@
         <v>5.6449</v>
       </c>
       <c r="F6" t="n">
-        <v>5.2223</v>
+        <v>4.9902</v>
       </c>
     </row>
     <row r="7">
@@ -581,7 +581,7 @@
         <v>6.593</v>
       </c>
       <c r="F7" t="n">
-        <v>5.8702</v>
+        <v>5.6059</v>
       </c>
     </row>
     <row r="8">
@@ -603,7 +603,7 @@
         <v>4605.379883</v>
       </c>
       <c r="F8" t="n">
-        <v>7722.720215</v>
+        <v>7785.040039</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         <v>15498.389648</v>
       </c>
       <c r="F9" t="n">
-        <v>27190.859375</v>
+        <v>27504.978516</v>
       </c>
     </row>
     <row r="10">
@@ -647,7 +647,7 @@
         <v>35819.558594</v>
       </c>
       <c r="F10" t="n">
-        <v>51176.960938</v>
+        <v>51352.410156</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>1783.900024</v>
       </c>
       <c r="F11" t="n">
-        <v>4162.299805</v>
+        <v>4167</v>
       </c>
     </row>
     <row r="12">
@@ -691,7 +691,7 @@
         <v>83.56999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>91.110001</v>
+        <v>88.980003</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>84.379997</v>
       </c>
       <c r="F13" t="n">
-        <v>102.25</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -735,7 +735,7 @@
         <v>1235.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1278.25</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +757,7 @@
         <v>568.25</v>
       </c>
       <c r="F15" t="n">
-        <v>497.75</v>
+        <v>497.5</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -471,7 +471,7 @@
         <v>103501</v>
       </c>
       <c r="F2" t="n">
-        <v>208982.96875</v>
+        <v>205427.203125</v>
       </c>
     </row>
     <row r="3">
@@ -493,7 +493,7 @@
         <v>99.68000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>205.960007</v>
+        <v>202.289993</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>111.199997</v>
       </c>
       <c r="F4" t="n">
-        <v>128.25</v>
+        <v>128.529999</v>
       </c>
     </row>
     <row r="5">
@@ -537,7 +537,7 @@
         <v>283</v>
       </c>
       <c r="F5" t="n">
-        <v>439.059998</v>
+        <v>440.369995</v>
       </c>
     </row>
     <row r="6">
@@ -559,7 +559,7 @@
         <v>5.6449</v>
       </c>
       <c r="F6" t="n">
-        <v>4.9902</v>
+        <v>4.9748</v>
       </c>
     </row>
     <row r="7">
@@ -581,7 +581,7 @@
         <v>6.593</v>
       </c>
       <c r="F7" t="n">
-        <v>5.6059</v>
+        <v>5.601</v>
       </c>
     </row>
     <row r="8">
@@ -603,7 +603,7 @@
         <v>4605.379883</v>
       </c>
       <c r="F8" t="n">
-        <v>7785.040039</v>
+        <v>7834.240234</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         <v>15498.389648</v>
       </c>
       <c r="F9" t="n">
-        <v>27504.978516</v>
+        <v>27662.966797</v>
       </c>
     </row>
     <row r="10">
@@ -647,7 +647,7 @@
         <v>35819.558594</v>
       </c>
       <c r="F10" t="n">
-        <v>51352.410156</v>
+        <v>51601.289062</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>1783.900024</v>
       </c>
       <c r="F11" t="n">
-        <v>4167</v>
+        <v>4191.299805</v>
       </c>
     </row>
     <row r="12">
@@ -691,7 +691,7 @@
         <v>83.56999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>88.980003</v>
+        <v>89.220001</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>84.379997</v>
       </c>
       <c r="F13" t="n">
-        <v>100</v>
+        <v>99.75</v>
       </c>
     </row>
     <row r="14">
@@ -735,7 +735,7 @@
         <v>1235.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1281</v>
+        <v>1295.75</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +757,7 @@
         <v>568.25</v>
       </c>
       <c r="F15" t="n">
-        <v>497.5</v>
+        <v>506.5</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -471,7 +471,7 @@
         <v>103501</v>
       </c>
       <c r="F2" t="n">
-        <v>205427.203125</v>
+        <v>204957.3125</v>
       </c>
     </row>
     <row r="3">
@@ -493,7 +493,7 @@
         <v>99.68000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>202.289993</v>
+        <v>201.839996</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>111.199997</v>
       </c>
       <c r="F4" t="n">
-        <v>128.529999</v>
+        <v>130.240005</v>
       </c>
     </row>
     <row r="5">
@@ -537,7 +537,7 @@
         <v>283</v>
       </c>
       <c r="F5" t="n">
-        <v>440.369995</v>
+        <v>439.339996</v>
       </c>
     </row>
     <row r="6">
@@ -559,7 +559,7 @@
         <v>5.6449</v>
       </c>
       <c r="F6" t="n">
-        <v>4.9748</v>
+        <v>4.9916</v>
       </c>
     </row>
     <row r="7">
@@ -581,7 +581,7 @@
         <v>6.593</v>
       </c>
       <c r="F7" t="n">
-        <v>5.601</v>
+        <v>5.5874</v>
       </c>
     </row>
     <row r="8">
@@ -603,7 +603,7 @@
         <v>4605.379883</v>
       </c>
       <c r="F8" t="n">
-        <v>7834.240234</v>
+        <v>7800.709961</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         <v>15498.389648</v>
       </c>
       <c r="F9" t="n">
-        <v>27662.966797</v>
+        <v>27498.011719</v>
       </c>
     </row>
     <row r="10">
@@ -647,7 +647,7 @@
         <v>35819.558594</v>
       </c>
       <c r="F10" t="n">
-        <v>51601.289062</v>
+        <v>51213.96875</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>1783.900024</v>
       </c>
       <c r="F11" t="n">
-        <v>4191.299805</v>
+        <v>4135.399902</v>
       </c>
     </row>
     <row r="12">
@@ -691,7 +691,7 @@
         <v>83.56999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>89.220001</v>
+        <v>88.779999</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>84.379997</v>
       </c>
       <c r="F13" t="n">
-        <v>99.75</v>
+        <v>100.699997</v>
       </c>
     </row>
     <row r="14">
@@ -735,7 +735,7 @@
         <v>1235.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1295.75</v>
+        <v>1293.5</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +757,7 @@
         <v>568.25</v>
       </c>
       <c r="F15" t="n">
-        <v>506.5</v>
+        <v>501.25</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -471,7 +471,7 @@
         <v>103501</v>
       </c>
       <c r="F2" t="n">
-        <v>204957.3125</v>
+        <v>205987.65625</v>
       </c>
     </row>
     <row r="3">
@@ -493,7 +493,7 @@
         <v>99.68000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>201.839996</v>
+        <v>202.75</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>111.199997</v>
       </c>
       <c r="F4" t="n">
-        <v>130.240005</v>
+        <v>133.270004</v>
       </c>
     </row>
     <row r="5">
@@ -537,7 +537,7 @@
         <v>283</v>
       </c>
       <c r="F5" t="n">
-        <v>439.339996</v>
+        <v>438.910004</v>
       </c>
     </row>
     <row r="6">
@@ -559,7 +559,7 @@
         <v>5.6449</v>
       </c>
       <c r="F6" t="n">
-        <v>4.9916</v>
+        <v>5.0122</v>
       </c>
     </row>
     <row r="7">
@@ -581,7 +581,7 @@
         <v>6.593</v>
       </c>
       <c r="F7" t="n">
-        <v>5.5874</v>
+        <v>5.6139</v>
       </c>
     </row>
     <row r="8">
@@ -603,7 +603,7 @@
         <v>4605.379883</v>
       </c>
       <c r="F8" t="n">
-        <v>7800.709961</v>
+        <v>7747.589844</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         <v>15498.389648</v>
       </c>
       <c r="F9" t="n">
-        <v>27498.011719</v>
+        <v>27173.046875</v>
       </c>
     </row>
     <row r="10">
@@ -647,7 +647,7 @@
         <v>35819.558594</v>
       </c>
       <c r="F10" t="n">
-        <v>51213.96875</v>
+        <v>51085.648438</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>1783.900024</v>
       </c>
       <c r="F11" t="n">
-        <v>4135.399902</v>
+        <v>4147.5</v>
       </c>
     </row>
     <row r="12">
@@ -691,7 +691,7 @@
         <v>83.56999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>88.779999</v>
+        <v>91.05999799999999</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>84.379997</v>
       </c>
       <c r="F13" t="n">
-        <v>100.699997</v>
+        <v>103.629997</v>
       </c>
     </row>
     <row r="14">
@@ -735,7 +735,7 @@
         <v>1235.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1293.5</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +757,7 @@
         <v>568.25</v>
       </c>
       <c r="F15" t="n">
-        <v>501.25</v>
+        <v>500</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -471,7 +471,7 @@
         <v>103501</v>
       </c>
       <c r="F2" t="n">
-        <v>205987.65625</v>
+        <v>206768.96875</v>
       </c>
     </row>
     <row r="3">
@@ -493,7 +493,7 @@
         <v>99.68000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>202.75</v>
+        <v>203.580002</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>111.199997</v>
       </c>
       <c r="F4" t="n">
-        <v>133.270004</v>
+        <v>133.729996</v>
       </c>
     </row>
     <row r="5">
@@ -537,7 +537,7 @@
         <v>283</v>
       </c>
       <c r="F5" t="n">
-        <v>438.910004</v>
+        <v>438.649994</v>
       </c>
     </row>
     <row r="6">
@@ -559,7 +559,7 @@
         <v>5.6449</v>
       </c>
       <c r="F6" t="n">
-        <v>5.0122</v>
+        <v>5.0001</v>
       </c>
     </row>
     <row r="7">
@@ -581,7 +581,7 @@
         <v>6.593</v>
       </c>
       <c r="F7" t="n">
-        <v>5.6139</v>
+        <v>5.6081</v>
       </c>
     </row>
     <row r="8">
@@ -603,7 +603,7 @@
         <v>4605.379883</v>
       </c>
       <c r="F8" t="n">
-        <v>7747.589844</v>
+        <v>7758.700195</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         <v>15498.389648</v>
       </c>
       <c r="F9" t="n">
-        <v>27173.046875</v>
+        <v>27225.183594</v>
       </c>
     </row>
     <row r="10">
@@ -647,7 +647,7 @@
         <v>35819.558594</v>
       </c>
       <c r="F10" t="n">
-        <v>51085.648438</v>
+        <v>51122.460938</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>1783.900024</v>
       </c>
       <c r="F11" t="n">
-        <v>4147.5</v>
+        <v>4157.899902</v>
       </c>
     </row>
     <row r="12">
@@ -691,7 +691,7 @@
         <v>83.56999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>91.05999799999999</v>
+        <v>90.800003</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>84.379997</v>
       </c>
       <c r="F13" t="n">
-        <v>103.629997</v>
+        <v>103.290001</v>
       </c>
     </row>
     <row r="14">
@@ -735,7 +735,7 @@
         <v>1235.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1288</v>
+        <v>1287.75</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +757,7 @@
         <v>568.25</v>
       </c>
       <c r="F15" t="n">
-        <v>500</v>
+        <v>500.5</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -471,7 +471,7 @@
         <v>103501</v>
       </c>
       <c r="F2" t="n">
-        <v>206768.96875</v>
+        <v>208674.40625</v>
       </c>
     </row>
     <row r="3">
@@ -493,7 +493,7 @@
         <v>99.68000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>203.580002</v>
+        <v>205.360001</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>111.199997</v>
       </c>
       <c r="F4" t="n">
-        <v>133.729996</v>
+        <v>138.789993</v>
       </c>
     </row>
     <row r="5">
@@ -537,7 +537,7 @@
         <v>283</v>
       </c>
       <c r="F5" t="n">
-        <v>438.649994</v>
+        <v>439.200012</v>
       </c>
     </row>
     <row r="6">
@@ -559,7 +559,7 @@
         <v>5.6449</v>
       </c>
       <c r="F6" t="n">
-        <v>5.0001</v>
+        <v>4.9842</v>
       </c>
     </row>
     <row r="7">
@@ -581,7 +581,7 @@
         <v>6.593</v>
       </c>
       <c r="F7" t="n">
-        <v>5.6081</v>
+        <v>5.577</v>
       </c>
     </row>
     <row r="8">
@@ -603,7 +603,7 @@
         <v>4605.379883</v>
       </c>
       <c r="F8" t="n">
-        <v>7758.700195</v>
+        <v>7807.779785</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         <v>15498.389648</v>
       </c>
       <c r="F9" t="n">
-        <v>27225.183594</v>
+        <v>27350.091797</v>
       </c>
     </row>
     <row r="10">
@@ -647,7 +647,7 @@
         <v>35819.558594</v>
       </c>
       <c r="F10" t="n">
-        <v>51122.460938</v>
+        <v>51618.488281</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>1783.900024</v>
       </c>
       <c r="F11" t="n">
-        <v>4157.899902</v>
+        <v>4210.899902</v>
       </c>
     </row>
     <row r="12">
@@ -691,7 +691,7 @@
         <v>83.56999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>90.800003</v>
+        <v>91.480003</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>84.379997</v>
       </c>
       <c r="F13" t="n">
-        <v>103.290001</v>
+        <v>104.099998</v>
       </c>
     </row>
     <row r="14">
@@ -735,7 +735,7 @@
         <v>1235.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1287.75</v>
+        <v>1274.5</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +757,7 @@
         <v>568.25</v>
       </c>
       <c r="F15" t="n">
-        <v>500.5</v>
+        <v>472.5</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -471,7 +471,7 @@
         <v>103501</v>
       </c>
       <c r="F2" t="n">
-        <v>208674.40625</v>
+        <v>208473.4375</v>
       </c>
     </row>
     <row r="3">
@@ -493,7 +493,7 @@
         <v>99.68000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>205.360001</v>
+        <v>205.149994</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>111.199997</v>
       </c>
       <c r="F4" t="n">
-        <v>138.789993</v>
+        <v>138.770004</v>
       </c>
     </row>
     <row r="5">
@@ -537,7 +537,7 @@
         <v>283</v>
       </c>
       <c r="F5" t="n">
-        <v>439.200012</v>
+        <v>439.23999</v>
       </c>
     </row>
     <row r="6">
@@ -559,7 +559,7 @@
         <v>5.6449</v>
       </c>
       <c r="F6" t="n">
-        <v>4.9842</v>
+        <v>4.9872</v>
       </c>
     </row>
     <row r="7">
@@ -581,7 +581,7 @@
         <v>6.593</v>
       </c>
       <c r="F7" t="n">
-        <v>5.577</v>
+        <v>5.5779</v>
       </c>
     </row>
     <row r="8">
@@ -603,7 +603,7 @@
         <v>4605.379883</v>
       </c>
       <c r="F8" t="n">
-        <v>7807.779785</v>
+        <v>7812.879883</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         <v>15498.389648</v>
       </c>
       <c r="F9" t="n">
-        <v>27350.091797</v>
+        <v>27376.107422</v>
       </c>
     </row>
     <row r="10">
@@ -647,7 +647,7 @@
         <v>35819.558594</v>
       </c>
       <c r="F10" t="n">
-        <v>51618.488281</v>
+        <v>51627.800781</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>1783.900024</v>
       </c>
       <c r="F11" t="n">
-        <v>4210.899902</v>
+        <v>4214.100098</v>
       </c>
     </row>
     <row r="12">
@@ -691,7 +691,7 @@
         <v>83.56999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>91.480003</v>
+        <v>91.199997</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>84.379997</v>
       </c>
       <c r="F13" t="n">
-        <v>104.099998</v>
+        <v>103.879997</v>
       </c>
     </row>
     <row r="14">
@@ -735,7 +735,7 @@
         <v>1235.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1274.5</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +757,7 @@
         <v>568.25</v>
       </c>
       <c r="F15" t="n">
-        <v>472.5</v>
+        <v>470.25</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -471,7 +471,7 @@
         <v>103501</v>
       </c>
       <c r="F2" t="n">
-        <v>208473.4375</v>
+        <v>209067</v>
       </c>
     </row>
     <row r="3">
@@ -493,7 +493,7 @@
         <v>99.68000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>205.149994</v>
+        <v>203.080002</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>111.199997</v>
       </c>
       <c r="F4" t="n">
-        <v>138.770004</v>
+        <v>134.389999</v>
       </c>
     </row>
     <row r="5">
@@ -537,7 +537,7 @@
         <v>283</v>
       </c>
       <c r="F5" t="n">
-        <v>439.23999</v>
+        <v>440.350006</v>
       </c>
     </row>
     <row r="6">
@@ -559,7 +559,7 @@
         <v>5.6449</v>
       </c>
       <c r="F6" t="n">
-        <v>4.9872</v>
+        <v>4.9772</v>
       </c>
     </row>
     <row r="7">
@@ -581,7 +581,7 @@
         <v>6.593</v>
       </c>
       <c r="F7" t="n">
-        <v>5.5779</v>
+        <v>5.5828</v>
       </c>
     </row>
     <row r="8">
@@ -603,7 +603,7 @@
         <v>4605.379883</v>
       </c>
       <c r="F8" t="n">
-        <v>7812.879883</v>
+        <v>7811.540039</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         <v>15498.389648</v>
       </c>
       <c r="F9" t="n">
-        <v>27376.107422</v>
+        <v>27366.169922</v>
       </c>
     </row>
     <row r="10">
@@ -647,7 +647,7 @@
         <v>35819.558594</v>
       </c>
       <c r="F10" t="n">
-        <v>51627.800781</v>
+        <v>51654.949219</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>1783.900024</v>
       </c>
       <c r="F11" t="n">
-        <v>4214.100098</v>
+        <v>4216.299805</v>
       </c>
     </row>
     <row r="12">
@@ -691,7 +691,7 @@
         <v>83.56999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>91.199997</v>
+        <v>91.849998</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>84.379997</v>
       </c>
       <c r="F13" t="n">
-        <v>103.879997</v>
+        <v>104.720001</v>
       </c>
     </row>
     <row r="14">
@@ -735,7 +735,7 @@
         <v>1235.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1273</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +757,7 @@
         <v>568.25</v>
       </c>
       <c r="F15" t="n">
-        <v>470.25</v>
+        <v>479.75</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -493,7 +493,7 @@
         <v>99.68000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>203.080002</v>
+        <v>205.550003</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>111.199997</v>
       </c>
       <c r="F4" t="n">
-        <v>134.389999</v>
+        <v>139.800003</v>
       </c>
     </row>
     <row r="5">
@@ -537,7 +537,7 @@
         <v>283</v>
       </c>
       <c r="F5" t="n">
-        <v>440.350006</v>
+        <v>439.25</v>
       </c>
     </row>
     <row r="6">
@@ -559,7 +559,7 @@
         <v>5.6449</v>
       </c>
       <c r="F6" t="n">
-        <v>4.9772</v>
+        <v>4.9918</v>
       </c>
     </row>
     <row r="7">

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -559,7 +559,7 @@
         <v>5.6449</v>
       </c>
       <c r="F6" t="n">
-        <v>4.9918</v>
+        <v>4.9863</v>
       </c>
     </row>
     <row r="7">
@@ -581,7 +581,7 @@
         <v>6.593</v>
       </c>
       <c r="F7" t="n">
-        <v>5.5828</v>
+        <v>5.5628</v>
       </c>
     </row>
     <row r="8">
@@ -603,7 +603,7 @@
         <v>4605.379883</v>
       </c>
       <c r="F8" t="n">
-        <v>7811.540039</v>
+        <v>7801.430176</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         <v>15498.389648</v>
       </c>
       <c r="F9" t="n">
-        <v>27366.169922</v>
+        <v>27238.013672</v>
       </c>
     </row>
     <row r="10">
@@ -647,7 +647,7 @@
         <v>35819.558594</v>
       </c>
       <c r="F10" t="n">
-        <v>51654.949219</v>
+        <v>51815.429688</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>1783.900024</v>
       </c>
       <c r="F11" t="n">
-        <v>4216.299805</v>
+        <v>4188.399902</v>
       </c>
     </row>
     <row r="12">
@@ -691,7 +691,7 @@
         <v>83.56999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>91.849998</v>
+        <v>93.55999799999999</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>84.379997</v>
       </c>
       <c r="F13" t="n">
-        <v>104.720001</v>
+        <v>106.470001</v>
       </c>
     </row>
     <row r="14">
@@ -735,7 +735,7 @@
         <v>1235.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1292</v>
+        <v>1288.25</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +757,7 @@
         <v>568.25</v>
       </c>
       <c r="F15" t="n">
-        <v>479.75</v>
+        <v>483.5</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -603,7 +603,7 @@
         <v>4605.379883</v>
       </c>
       <c r="F8" t="n">
-        <v>7801.430176</v>
+        <v>7805.220215</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         <v>15498.389648</v>
       </c>
       <c r="F9" t="n">
-        <v>27238.013672</v>
+        <v>27254.84375</v>
       </c>
     </row>
     <row r="10">
@@ -647,7 +647,7 @@
         <v>35819.558594</v>
       </c>
       <c r="F10" t="n">
-        <v>51815.429688</v>
+        <v>51821.851562</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>1783.900024</v>
       </c>
       <c r="F11" t="n">
-        <v>4188.399902</v>
+        <v>4192</v>
       </c>
     </row>
     <row r="12">
@@ -691,7 +691,7 @@
         <v>83.56999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>93.55999799999999</v>
+        <v>93.540001</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>84.379997</v>
       </c>
       <c r="F13" t="n">
-        <v>106.470001</v>
+        <v>106.489998</v>
       </c>
     </row>
     <row r="14">

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -471,7 +471,7 @@
         <v>103501</v>
       </c>
       <c r="F2" t="n">
-        <v>209067</v>
+        <v>206741.546875</v>
       </c>
     </row>
     <row r="3">
@@ -493,7 +493,7 @@
         <v>99.68000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>205.550003</v>
+        <v>203.5</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>111.199997</v>
       </c>
       <c r="F4" t="n">
-        <v>139.800003</v>
+        <v>135.210007</v>
       </c>
     </row>
     <row r="5">
@@ -537,7 +537,7 @@
         <v>283</v>
       </c>
       <c r="F5" t="n">
-        <v>439.25</v>
+        <v>441.290009</v>
       </c>
     </row>
     <row r="6">
@@ -559,7 +559,7 @@
         <v>5.6449</v>
       </c>
       <c r="F6" t="n">
-        <v>4.9863</v>
+        <v>5.0137</v>
       </c>
     </row>
     <row r="7">
@@ -581,7 +581,7 @@
         <v>6.593</v>
       </c>
       <c r="F7" t="n">
-        <v>5.5628</v>
+        <v>5.6095</v>
       </c>
     </row>
     <row r="8">
@@ -603,7 +603,7 @@
         <v>4605.379883</v>
       </c>
       <c r="F8" t="n">
-        <v>7805.220215</v>
+        <v>7797.970215</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         <v>15498.389648</v>
       </c>
       <c r="F9" t="n">
-        <v>27254.84375</v>
+        <v>27187.478516</v>
       </c>
     </row>
     <row r="10">
@@ -647,7 +647,7 @@
         <v>35819.558594</v>
       </c>
       <c r="F10" t="n">
-        <v>51821.851562</v>
+        <v>51644.039062</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>1783.900024</v>
       </c>
       <c r="F11" t="n">
-        <v>4192</v>
+        <v>4177.399902</v>
       </c>
     </row>
     <row r="12">
@@ -691,7 +691,7 @@
         <v>83.56999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>93.540001</v>
+        <v>94.290001</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>84.379997</v>
       </c>
       <c r="F13" t="n">
-        <v>106.489998</v>
+        <v>105.959999</v>
       </c>
     </row>
     <row r="14">
@@ -735,7 +735,7 @@
         <v>1235.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1288.25</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +757,7 @@
         <v>568.25</v>
       </c>
       <c r="F15" t="n">
-        <v>483.5</v>
+        <v>482.5</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -471,7 +471,7 @@
         <v>103501</v>
       </c>
       <c r="F2" t="n">
-        <v>206741.546875</v>
+        <v>204498.546875</v>
       </c>
     </row>
     <row r="3">
@@ -493,7 +493,7 @@
         <v>99.68000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>203.5</v>
+        <v>201.429993</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>111.199997</v>
       </c>
       <c r="F4" t="n">
-        <v>135.210007</v>
+        <v>131.199997</v>
       </c>
     </row>
     <row r="5">
@@ -537,7 +537,7 @@
         <v>283</v>
       </c>
       <c r="F5" t="n">
-        <v>441.290009</v>
+        <v>441.929993</v>
       </c>
     </row>
     <row r="6">
@@ -559,7 +559,7 @@
         <v>5.6449</v>
       </c>
       <c r="F6" t="n">
-        <v>5.0137</v>
+        <v>5.0395</v>
       </c>
     </row>
     <row r="7">
@@ -581,7 +581,7 @@
         <v>6.593</v>
       </c>
       <c r="F7" t="n">
-        <v>5.6095</v>
+        <v>5.6045</v>
       </c>
     </row>
     <row r="8">
@@ -603,7 +603,7 @@
         <v>4605.379883</v>
       </c>
       <c r="F8" t="n">
-        <v>7797.970215</v>
+        <v>7748.819824</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         <v>15498.389648</v>
       </c>
       <c r="F9" t="n">
-        <v>27187.478516</v>
+        <v>26954.634766</v>
       </c>
     </row>
     <row r="10">
@@ -647,7 +647,7 @@
         <v>35819.558594</v>
       </c>
       <c r="F10" t="n">
-        <v>51644.039062</v>
+        <v>51627.679688</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>1783.900024</v>
       </c>
       <c r="F11" t="n">
-        <v>4177.399902</v>
+        <v>4118.200195</v>
       </c>
     </row>
     <row r="12">
@@ -691,7 +691,7 @@
         <v>83.56999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>94.290001</v>
+        <v>95.31999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>84.379997</v>
       </c>
       <c r="F13" t="n">
-        <v>105.959999</v>
+        <v>105.910004</v>
       </c>
     </row>
     <row r="14">
@@ -735,7 +735,7 @@
         <v>1235.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1284</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +757,7 @@
         <v>568.25</v>
       </c>
       <c r="F15" t="n">
-        <v>482.5</v>
+        <v>480</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -471,7 +471,7 @@
         <v>103501</v>
       </c>
       <c r="F2" t="n">
-        <v>204498.546875</v>
+        <v>204599.5</v>
       </c>
     </row>
     <row r="3">
@@ -493,7 +493,7 @@
         <v>99.68000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>201.429993</v>
+        <v>201.509995</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>111.199997</v>
       </c>
       <c r="F4" t="n">
-        <v>131.199997</v>
+        <v>130.940002</v>
       </c>
     </row>
     <row r="5">
@@ -537,7 +537,7 @@
         <v>283</v>
       </c>
       <c r="F5" t="n">
-        <v>441.929993</v>
+        <v>441.399994</v>
       </c>
     </row>
     <row r="6">
@@ -559,7 +559,7 @@
         <v>5.6449</v>
       </c>
       <c r="F6" t="n">
-        <v>5.0395</v>
+        <v>5.0385</v>
       </c>
     </row>
     <row r="7">
@@ -581,7 +581,7 @@
         <v>6.593</v>
       </c>
       <c r="F7" t="n">
-        <v>5.6045</v>
+        <v>5.607</v>
       </c>
     </row>
     <row r="8">
@@ -603,7 +603,7 @@
         <v>4605.379883</v>
       </c>
       <c r="F8" t="n">
-        <v>7748.819824</v>
+        <v>7748.359863</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         <v>15498.389648</v>
       </c>
       <c r="F9" t="n">
-        <v>26954.634766</v>
+        <v>26941.662109</v>
       </c>
     </row>
     <row r="10">
@@ -647,7 +647,7 @@
         <v>35819.558594</v>
       </c>
       <c r="F10" t="n">
-        <v>51627.679688</v>
+        <v>51619.429688</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>1783.900024</v>
       </c>
       <c r="F11" t="n">
-        <v>4118.200195</v>
+        <v>4125.299805</v>
       </c>
     </row>
     <row r="12">
@@ -691,7 +691,7 @@
         <v>83.56999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>95.31999999999999</v>
+        <v>94.93000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>84.379997</v>
       </c>
       <c r="F13" t="n">
-        <v>105.910004</v>
+        <v>105.650002</v>
       </c>
     </row>
     <row r="14">
@@ -735,7 +735,7 @@
         <v>1235.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1278</v>
+        <v>1278.25</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +757,7 @@
         <v>568.25</v>
       </c>
       <c r="F15" t="n">
-        <v>480</v>
+        <v>479.75</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -471,7 +471,7 @@
         <v>103501</v>
       </c>
       <c r="F2" t="n">
-        <v>204599.5</v>
+        <v>205512.375</v>
       </c>
     </row>
     <row r="3">
@@ -493,7 +493,7 @@
         <v>99.68000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>201.509995</v>
+        <v>202.300003</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>111.199997</v>
       </c>
       <c r="F4" t="n">
-        <v>130.940002</v>
+        <v>132.309998</v>
       </c>
     </row>
     <row r="5">
@@ -537,7 +537,7 @@
         <v>283</v>
       </c>
       <c r="F5" t="n">
-        <v>441.399994</v>
+        <v>438.640015</v>
       </c>
     </row>
     <row r="6">
@@ -559,7 +559,7 @@
         <v>5.6449</v>
       </c>
       <c r="F6" t="n">
-        <v>5.0385</v>
+        <v>5.0463</v>
       </c>
     </row>
     <row r="7">
@@ -581,7 +581,7 @@
         <v>6.593</v>
       </c>
       <c r="F7" t="n">
-        <v>5.607</v>
+        <v>5.6621</v>
       </c>
     </row>
     <row r="8">
@@ -603,7 +603,7 @@
         <v>4605.379883</v>
       </c>
       <c r="F8" t="n">
-        <v>7748.359863</v>
+        <v>7697.810059</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         <v>15498.389648</v>
       </c>
       <c r="F9" t="n">
-        <v>26941.662109</v>
+        <v>26452.943359</v>
       </c>
     </row>
     <row r="10">
@@ -647,7 +647,7 @@
         <v>35819.558594</v>
       </c>
       <c r="F10" t="n">
-        <v>51619.429688</v>
+        <v>51953.851562</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>1783.900024</v>
       </c>
       <c r="F11" t="n">
-        <v>4125.299805</v>
+        <v>4180.600098</v>
       </c>
     </row>
     <row r="12">
@@ -691,7 +691,7 @@
         <v>83.56999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>94.93000000000001</v>
+        <v>95.040001</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>84.379997</v>
       </c>
       <c r="F13" t="n">
-        <v>105.650002</v>
+        <v>105.209999</v>
       </c>
     </row>
     <row r="14">
@@ -735,7 +735,7 @@
         <v>1235.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1278.25</v>
+        <v>1274.75</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +757,7 @@
         <v>568.25</v>
       </c>
       <c r="F15" t="n">
-        <v>479.75</v>
+        <v>480.25</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -471,7 +471,7 @@
         <v>103501</v>
       </c>
       <c r="F2" t="n">
-        <v>205512.375</v>
+        <v>205726.09375</v>
       </c>
     </row>
     <row r="3">
@@ -493,7 +493,7 @@
         <v>99.68000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>202.300003</v>
+        <v>202.639999</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>111.199997</v>
       </c>
       <c r="F4" t="n">
-        <v>132.309998</v>
+        <v>131.389999</v>
       </c>
     </row>
     <row r="5">
@@ -537,7 +537,7 @@
         <v>283</v>
       </c>
       <c r="F5" t="n">
-        <v>438.640015</v>
+        <v>443.209991</v>
       </c>
     </row>
     <row r="6">
@@ -559,7 +559,7 @@
         <v>5.6449</v>
       </c>
       <c r="F6" t="n">
-        <v>5.0463</v>
+        <v>5.0767</v>
       </c>
     </row>
     <row r="7">
@@ -581,7 +581,7 @@
         <v>6.593</v>
       </c>
       <c r="F7" t="n">
-        <v>5.6621</v>
+        <v>5.7122</v>
       </c>
     </row>
     <row r="8">
@@ -603,7 +603,7 @@
         <v>4605.379883</v>
       </c>
       <c r="F8" t="n">
-        <v>7697.810059</v>
+        <v>7733.080078</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         <v>15498.389648</v>
       </c>
       <c r="F9" t="n">
-        <v>26452.943359</v>
+        <v>26499.583984</v>
       </c>
     </row>
     <row r="10">
@@ -647,7 +647,7 @@
         <v>35819.558594</v>
       </c>
       <c r="F10" t="n">
-        <v>51953.851562</v>
+        <v>52400.160156</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>1783.900024</v>
       </c>
       <c r="F11" t="n">
-        <v>4180.600098</v>
+        <v>4207.799805</v>
       </c>
     </row>
     <row r="12">
@@ -691,7 +691,7 @@
         <v>83.56999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>95.040001</v>
+        <v>95.589996</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>84.379997</v>
       </c>
       <c r="F13" t="n">
-        <v>105.209999</v>
+        <v>105.459999</v>
       </c>
     </row>
     <row r="14">
@@ -735,7 +735,7 @@
         <v>1235.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1274.75</v>
+        <v>1253.75</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +757,7 @@
         <v>568.25</v>
       </c>
       <c r="F15" t="n">
-        <v>480.25</v>
+        <v>473.75</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -471,7 +471,7 @@
         <v>103501</v>
       </c>
       <c r="F2" t="n">
-        <v>205726.09375</v>
+        <v>205430</v>
       </c>
     </row>
     <row r="3">
@@ -493,7 +493,7 @@
         <v>99.68000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>202.639999</v>
+        <v>201.389999</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>111.199997</v>
       </c>
       <c r="F4" t="n">
-        <v>131.389999</v>
+        <v>130.830002</v>
       </c>
     </row>
     <row r="5">
@@ -537,7 +537,7 @@
         <v>283</v>
       </c>
       <c r="F5" t="n">
-        <v>443.209991</v>
+        <v>444.450012</v>
       </c>
     </row>
     <row r="6">
@@ -559,7 +559,7 @@
         <v>5.6449</v>
       </c>
       <c r="F6" t="n">
-        <v>5.0767</v>
+        <v>5.0693</v>
       </c>
     </row>
     <row r="7">
@@ -581,7 +581,7 @@
         <v>6.593</v>
       </c>
       <c r="F7" t="n">
-        <v>5.7122</v>
+        <v>5.7053</v>
       </c>
     </row>
     <row r="8">
@@ -603,7 +603,7 @@
         <v>4605.379883</v>
       </c>
       <c r="F8" t="n">
-        <v>7733.080078</v>
+        <v>7659.439941</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         <v>15498.389648</v>
       </c>
       <c r="F9" t="n">
-        <v>26499.583984</v>
+        <v>26140.029297</v>
       </c>
     </row>
     <row r="10">
@@ -647,7 +647,7 @@
         <v>35819.558594</v>
       </c>
       <c r="F10" t="n">
-        <v>52400.160156</v>
+        <v>52002.410156</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>1783.900024</v>
       </c>
       <c r="F11" t="n">
-        <v>4207.799805</v>
+        <v>4181.100098</v>
       </c>
     </row>
     <row r="12">
@@ -691,7 +691,7 @@
         <v>83.56999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>95.589996</v>
+        <v>101.410004</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>84.379997</v>
       </c>
       <c r="F13" t="n">
-        <v>105.459999</v>
+        <v>109.860001</v>
       </c>
     </row>
     <row r="14">
@@ -735,7 +735,7 @@
         <v>1235.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1253.75</v>
+        <v>1261.25</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +757,7 @@
         <v>568.25</v>
       </c>
       <c r="F15" t="n">
-        <v>473.75</v>
+        <v>474.25</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -493,7 +493,7 @@
         <v>99.68000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>201.389999</v>
+        <v>202.300003</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>111.199997</v>
       </c>
       <c r="F4" t="n">
-        <v>130.830002</v>
+        <v>131</v>
       </c>
     </row>
     <row r="5">
@@ -537,7 +537,7 @@
         <v>283</v>
       </c>
       <c r="F5" t="n">
-        <v>444.450012</v>
+        <v>438.549988</v>
       </c>
     </row>
     <row r="6">
@@ -568,21 +568,13 @@
           <t>euro_real</t>
         </is>
       </c>
-      <c r="B7" s="1" t="n">
-        <v>44500</v>
-      </c>
-      <c r="C7" s="1" t="n">
-        <v>46326</v>
-      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>61</v>
-      </c>
-      <c r="E7" t="n">
-        <v>6.593</v>
-      </c>
-      <c r="F7" t="n">
-        <v>5.7053</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -691,7 +683,7 @@
         <v>83.56999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>101.410004</v>
+        <v>99.019997</v>
       </c>
     </row>
     <row r="13">

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -471,7 +471,7 @@
         <v>103501</v>
       </c>
       <c r="F2" t="n">
-        <v>205430</v>
+        <v>204667.15625</v>
       </c>
     </row>
     <row r="3">
@@ -493,7 +493,7 @@
         <v>99.68000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>202.300003</v>
+        <v>201.429993</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>111.199997</v>
       </c>
       <c r="F4" t="n">
-        <v>131</v>
+        <v>133.410004</v>
       </c>
     </row>
     <row r="5">
@@ -537,7 +537,7 @@
         <v>283</v>
       </c>
       <c r="F5" t="n">
-        <v>438.549988</v>
+        <v>440.230011</v>
       </c>
     </row>
     <row r="6">
@@ -559,7 +559,7 @@
         <v>5.6449</v>
       </c>
       <c r="F6" t="n">
-        <v>5.0693</v>
+        <v>5.0579</v>
       </c>
     </row>
     <row r="7">
@@ -568,13 +568,21 @@
           <t>euro_real</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
+      <c r="B7" s="1" t="n">
+        <v>44500</v>
+      </c>
+      <c r="C7" s="1" t="n">
+        <v>46326</v>
+      </c>
       <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
+        <v>61</v>
+      </c>
+      <c r="E7" t="n">
+        <v>6.593</v>
+      </c>
+      <c r="F7" t="n">
+        <v>5.673</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -595,7 +603,7 @@
         <v>4605.379883</v>
       </c>
       <c r="F8" t="n">
-        <v>7659.439941</v>
+        <v>7708.77002</v>
       </c>
     </row>
     <row r="9">
@@ -617,7 +625,7 @@
         <v>15498.389648</v>
       </c>
       <c r="F9" t="n">
-        <v>26140.029297</v>
+        <v>26522.501953</v>
       </c>
     </row>
     <row r="10">
@@ -639,7 +647,7 @@
         <v>35819.558594</v>
       </c>
       <c r="F10" t="n">
-        <v>52002.410156</v>
+        <v>52020.359375</v>
       </c>
     </row>
     <row r="11">
@@ -661,7 +669,7 @@
         <v>1783.900024</v>
       </c>
       <c r="F11" t="n">
-        <v>4181.100098</v>
+        <v>4161.899902</v>
       </c>
     </row>
     <row r="12">
@@ -683,7 +691,7 @@
         <v>83.56999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>99.019997</v>
+        <v>98.599998</v>
       </c>
     </row>
     <row r="13">
@@ -705,7 +713,7 @@
         <v>84.379997</v>
       </c>
       <c r="F13" t="n">
-        <v>109.860001</v>
+        <v>109.400002</v>
       </c>
     </row>
     <row r="14">
@@ -727,7 +735,7 @@
         <v>1235.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1261.25</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="15">
@@ -749,7 +757,7 @@
         <v>568.25</v>
       </c>
       <c r="F15" t="n">
-        <v>474.25</v>
+        <v>467.75</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -471,7 +471,7 @@
         <v>103501</v>
       </c>
       <c r="F2" t="n">
-        <v>204667.15625</v>
+        <v>207377.765625</v>
       </c>
     </row>
     <row r="3">
@@ -493,7 +493,7 @@
         <v>99.68000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>201.429993</v>
+        <v>204.220001</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>111.199997</v>
       </c>
       <c r="F4" t="n">
-        <v>133.410004</v>
+        <v>137.440002</v>
       </c>
     </row>
     <row r="5">
@@ -537,7 +537,7 @@
         <v>283</v>
       </c>
       <c r="F5" t="n">
-        <v>440.230011</v>
+        <v>437.529999</v>
       </c>
     </row>
     <row r="6">
@@ -559,7 +559,7 @@
         <v>5.6449</v>
       </c>
       <c r="F6" t="n">
-        <v>5.0579</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="7">
@@ -581,7 +581,7 @@
         <v>6.593</v>
       </c>
       <c r="F7" t="n">
-        <v>5.673</v>
+        <v>5.6383</v>
       </c>
     </row>
     <row r="8">
@@ -603,7 +603,7 @@
         <v>4605.379883</v>
       </c>
       <c r="F8" t="n">
-        <v>7708.77002</v>
+        <v>7736.75</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         <v>15498.389648</v>
       </c>
       <c r="F9" t="n">
-        <v>26522.501953</v>
+        <v>26544.773438</v>
       </c>
     </row>
     <row r="10">
@@ -647,7 +647,7 @@
         <v>35819.558594</v>
       </c>
       <c r="F10" t="n">
-        <v>52020.359375</v>
+        <v>52561.949219</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>1783.900024</v>
       </c>
       <c r="F11" t="n">
-        <v>4161.899902</v>
+        <v>4169.299805</v>
       </c>
     </row>
     <row r="12">
@@ -691,7 +691,7 @@
         <v>83.56999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>98.599998</v>
+        <v>96.30999799999999</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>84.379997</v>
       </c>
       <c r="F13" t="n">
-        <v>109.400002</v>
+        <v>107</v>
       </c>
     </row>
     <row r="14">
@@ -735,7 +735,7 @@
         <v>1235.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1251</v>
+        <v>1253.25</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +757,7 @@
         <v>568.25</v>
       </c>
       <c r="F15" t="n">
-        <v>467.75</v>
+        <v>462.75</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -471,7 +471,7 @@
         <v>103501</v>
       </c>
       <c r="F2" t="n">
-        <v>207377.765625</v>
+        <v>207602.875</v>
       </c>
     </row>
     <row r="3">
@@ -493,7 +493,7 @@
         <v>99.68000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>204.220001</v>
+        <v>204.389999</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>111.199997</v>
       </c>
       <c r="F4" t="n">
-        <v>137.440002</v>
+        <v>137.669998</v>
       </c>
     </row>
     <row r="5">
@@ -537,7 +537,7 @@
         <v>283</v>
       </c>
       <c r="F5" t="n">
-        <v>437.529999</v>
+        <v>438.600006</v>
       </c>
     </row>
     <row r="6">
@@ -559,7 +559,7 @@
         <v>5.6449</v>
       </c>
       <c r="F6" t="n">
-        <v>5.01</v>
+        <v>5.023</v>
       </c>
     </row>
     <row r="7">
@@ -581,7 +581,7 @@
         <v>6.593</v>
       </c>
       <c r="F7" t="n">
-        <v>5.6383</v>
+        <v>5.6414</v>
       </c>
     </row>
     <row r="8">
@@ -603,7 +603,7 @@
         <v>4605.379883</v>
       </c>
       <c r="F8" t="n">
-        <v>7736.75</v>
+        <v>7733.419922</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         <v>15498.389648</v>
       </c>
       <c r="F9" t="n">
-        <v>26544.773438</v>
+        <v>26607.212891</v>
       </c>
     </row>
     <row r="10">
@@ -647,7 +647,7 @@
         <v>35819.558594</v>
       </c>
       <c r="F10" t="n">
-        <v>52561.949219</v>
+        <v>52536.589844</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>1783.900024</v>
       </c>
       <c r="F11" t="n">
-        <v>4169.299805</v>
+        <v>4149.100098</v>
       </c>
     </row>
     <row r="12">
@@ -691,7 +691,7 @@
         <v>83.56999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>96.30999799999999</v>
+        <v>97.800003</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>84.379997</v>
       </c>
       <c r="F13" t="n">
-        <v>107</v>
+        <v>109.040001</v>
       </c>
     </row>
     <row r="14">
@@ -735,7 +735,7 @@
         <v>1235.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1253.25</v>
+        <v>1238.5</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +757,7 @@
         <v>568.25</v>
       </c>
       <c r="F15" t="n">
-        <v>462.75</v>
+        <v>456.25</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -471,7 +471,7 @@
         <v>103501</v>
       </c>
       <c r="F2" t="n">
-        <v>207602.875</v>
+        <v>203775.984375</v>
       </c>
     </row>
     <row r="3">
@@ -493,7 +493,7 @@
         <v>99.68000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>204.389999</v>
+        <v>200.619995</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>111.199997</v>
       </c>
       <c r="F4" t="n">
-        <v>137.669998</v>
+        <v>134.389999</v>
       </c>
     </row>
     <row r="5">
@@ -537,7 +537,7 @@
         <v>283</v>
       </c>
       <c r="F5" t="n">
-        <v>438.600006</v>
+        <v>435.700012</v>
       </c>
     </row>
     <row r="6">
@@ -559,7 +559,7 @@
         <v>5.6449</v>
       </c>
       <c r="F6" t="n">
-        <v>5.023</v>
+        <v>5.0487</v>
       </c>
     </row>
     <row r="7">
@@ -581,7 +581,7 @@
         <v>6.593</v>
       </c>
       <c r="F7" t="n">
-        <v>5.6414</v>
+        <v>5.6493</v>
       </c>
     </row>
     <row r="8">
@@ -603,7 +603,7 @@
         <v>4605.379883</v>
       </c>
       <c r="F8" t="n">
-        <v>7733.419922</v>
+        <v>7649.620117</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         <v>15498.389648</v>
       </c>
       <c r="F9" t="n">
-        <v>26607.212891</v>
+        <v>26096.677734</v>
       </c>
     </row>
     <row r="10">
@@ -647,7 +647,7 @@
         <v>35819.558594</v>
       </c>
       <c r="F10" t="n">
-        <v>52536.589844</v>
+        <v>52570.058594</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>1783.900024</v>
       </c>
       <c r="F11" t="n">
-        <v>4149.100098</v>
+        <v>4069.300049</v>
       </c>
     </row>
     <row r="12">
@@ -691,7 +691,7 @@
         <v>83.56999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>97.800003</v>
+        <v>98.410004</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>84.379997</v>
       </c>
       <c r="F13" t="n">
-        <v>109.040001</v>
+        <v>111.389999</v>
       </c>
     </row>
     <row r="14">
@@ -735,7 +735,7 @@
         <v>1235.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1238.5</v>
+        <v>1263.75</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +757,7 @@
         <v>568.25</v>
       </c>
       <c r="F15" t="n">
-        <v>456.25</v>
+        <v>459.75</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -471,7 +471,7 @@
         <v>103501</v>
       </c>
       <c r="F2" t="n">
-        <v>203775.984375</v>
+        <v>203917.265625</v>
       </c>
     </row>
     <row r="3">
@@ -493,7 +493,7 @@
         <v>99.68000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>200.619995</v>
+        <v>200.830002</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>111.199997</v>
       </c>
       <c r="F4" t="n">
-        <v>134.389999</v>
+        <v>134.300003</v>
       </c>
     </row>
     <row r="5">
@@ -537,7 +537,7 @@
         <v>283</v>
       </c>
       <c r="F5" t="n">
-        <v>435.700012</v>
+        <v>433.559998</v>
       </c>
     </row>
     <row r="6">
@@ -559,7 +559,7 @@
         <v>5.6449</v>
       </c>
       <c r="F6" t="n">
-        <v>5.0487</v>
+        <v>5.044</v>
       </c>
     </row>
     <row r="7">
@@ -581,7 +581,7 @@
         <v>6.593</v>
       </c>
       <c r="F7" t="n">
-        <v>5.6493</v>
+        <v>5.6461</v>
       </c>
     </row>
     <row r="8">
@@ -603,7 +603,7 @@
         <v>4605.379883</v>
       </c>
       <c r="F8" t="n">
-        <v>7649.620117</v>
+        <v>7620.830078</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         <v>15498.389648</v>
       </c>
       <c r="F9" t="n">
-        <v>26096.677734</v>
+        <v>25972.888672</v>
       </c>
     </row>
     <row r="10">
@@ -647,7 +647,7 @@
         <v>35819.558594</v>
       </c>
       <c r="F10" t="n">
-        <v>52570.058594</v>
+        <v>52102.460938</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>1783.900024</v>
       </c>
       <c r="F11" t="n">
-        <v>4069.300049</v>
+        <v>4010.300049</v>
       </c>
     </row>
     <row r="12">
@@ -691,7 +691,7 @@
         <v>83.56999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>98.410004</v>
+        <v>102.190002</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>84.379997</v>
       </c>
       <c r="F13" t="n">
-        <v>111.389999</v>
+        <v>111.139999</v>
       </c>
     </row>
     <row r="14">
@@ -735,7 +735,7 @@
         <v>1235.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1263.75</v>
+        <v>1271.75</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +757,7 @@
         <v>568.25</v>
       </c>
       <c r="F15" t="n">
-        <v>459.75</v>
+        <v>457.75</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -471,7 +471,7 @@
         <v>103501</v>
       </c>
       <c r="F2" t="n">
-        <v>203917.265625</v>
+        <v>205083</v>
       </c>
     </row>
     <row r="3">
@@ -493,7 +493,7 @@
         <v>99.68000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>200.830002</v>
+        <v>201.690002</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>111.199997</v>
       </c>
       <c r="F4" t="n">
-        <v>134.300003</v>
+        <v>137.160004</v>
       </c>
     </row>
     <row r="5">
@@ -537,7 +537,7 @@
         <v>283</v>
       </c>
       <c r="F5" t="n">
-        <v>433.559998</v>
+        <v>430</v>
       </c>
     </row>
     <row r="6">
@@ -559,7 +559,7 @@
         <v>5.6449</v>
       </c>
       <c r="F6" t="n">
-        <v>5.044</v>
+        <v>4.9964</v>
       </c>
     </row>
     <row r="7">
@@ -581,7 +581,7 @@
         <v>6.593</v>
       </c>
       <c r="F7" t="n">
-        <v>5.6461</v>
+        <v>5.5626</v>
       </c>
     </row>
     <row r="8">
@@ -603,7 +603,7 @@
         <v>4605.379883</v>
       </c>
       <c r="F8" t="n">
-        <v>7620.830078</v>
+        <v>7623.680176</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         <v>15498.389648</v>
       </c>
       <c r="F9" t="n">
-        <v>25972.888672</v>
+        <v>25955.339844</v>
       </c>
     </row>
     <row r="10">
@@ -647,7 +647,7 @@
         <v>35819.558594</v>
       </c>
       <c r="F10" t="n">
-        <v>52102.460938</v>
+        <v>52215.160156</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>1783.900024</v>
       </c>
       <c r="F11" t="n">
-        <v>4010.300049</v>
+        <v>4007.899902</v>
       </c>
     </row>
     <row r="12">
@@ -691,7 +691,7 @@
         <v>83.56999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>102.190002</v>
+        <v>103.269997</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>84.379997</v>
       </c>
       <c r="F13" t="n">
-        <v>111.139999</v>
+        <v>116.720001</v>
       </c>
     </row>
     <row r="14">
@@ -735,7 +735,7 @@
         <v>1235.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1271.75</v>
+        <v>1256.5</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +757,7 @@
         <v>568.25</v>
       </c>
       <c r="F15" t="n">
-        <v>457.75</v>
+        <v>456</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -559,7 +559,7 @@
         <v>5.6449</v>
       </c>
       <c r="F6" t="n">
-        <v>4.9964</v>
+        <v>4.9652</v>
       </c>
     </row>
     <row r="7">
@@ -713,7 +713,7 @@
         <v>84.379997</v>
       </c>
       <c r="F13" t="n">
-        <v>116.720001</v>
+        <v>111.699997</v>
       </c>
     </row>
     <row r="14">

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -471,7 +471,7 @@
         <v>103501</v>
       </c>
       <c r="F2" t="n">
-        <v>205083</v>
+        <v>173958.859375</v>
       </c>
     </row>
     <row r="3">
@@ -493,7 +493,7 @@
         <v>99.68000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>201.690002</v>
+        <v>170.990005</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>111.199997</v>
       </c>
       <c r="F4" t="n">
-        <v>137.160004</v>
+        <v>100.959999</v>
       </c>
     </row>
     <row r="5">
@@ -537,7 +537,7 @@
         <v>283</v>
       </c>
       <c r="F5" t="n">
-        <v>430</v>
+        <v>471.690002</v>
       </c>
     </row>
     <row r="6">
@@ -559,7 +559,7 @@
         <v>5.6449</v>
       </c>
       <c r="F6" t="n">
-        <v>4.9652</v>
+        <v>5.4467</v>
       </c>
     </row>
     <row r="7">
@@ -581,7 +581,7 @@
         <v>6.593</v>
       </c>
       <c r="F7" t="n">
-        <v>5.5626</v>
+        <v>6.0905</v>
       </c>
     </row>
     <row r="8">
@@ -603,7 +603,7 @@
         <v>4605.379883</v>
       </c>
       <c r="F8" t="n">
-        <v>7623.680176</v>
+        <v>7681.919922</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         <v>15498.389648</v>
       </c>
       <c r="F9" t="n">
-        <v>25955.339844</v>
+        <v>26216.0625</v>
       </c>
     </row>
     <row r="10">
@@ -647,7 +647,7 @@
         <v>35819.558594</v>
       </c>
       <c r="F10" t="n">
-        <v>52215.160156</v>
+        <v>52373.011719</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>1783.900024</v>
       </c>
       <c r="F11" t="n">
-        <v>4007.899902</v>
+        <v>4032.800049</v>
       </c>
     </row>
     <row r="12">
@@ -691,7 +691,7 @@
         <v>83.56999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>103.269997</v>
+        <v>102.870003</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>84.379997</v>
       </c>
       <c r="F13" t="n">
-        <v>111.699997</v>
+        <v>111.949997</v>
       </c>
     </row>
     <row r="14">
@@ -735,7 +735,7 @@
         <v>1235.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1256.5</v>
+        <v>1248.5</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +757,7 @@
         <v>568.25</v>
       </c>
       <c r="F15" t="n">
-        <v>456</v>
+        <v>454</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -471,7 +471,7 @@
         <v>103501</v>
       </c>
       <c r="F2" t="n">
-        <v>173958.859375</v>
+        <v>176027.578125</v>
       </c>
     </row>
     <row r="3">
@@ -493,7 +493,7 @@
         <v>99.68000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>170.990005</v>
+        <v>173.179993</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>111.199997</v>
       </c>
       <c r="F4" t="n">
-        <v>100.959999</v>
+        <v>100.730003</v>
       </c>
     </row>
     <row r="5">
@@ -537,7 +537,7 @@
         <v>283</v>
       </c>
       <c r="F5" t="n">
-        <v>471.690002</v>
+        <v>465.970001</v>
       </c>
     </row>
     <row r="6">
@@ -559,7 +559,7 @@
         <v>5.6449</v>
       </c>
       <c r="F6" t="n">
-        <v>5.4467</v>
+        <v>5.3271</v>
       </c>
     </row>
     <row r="7">
@@ -581,7 +581,7 @@
         <v>6.593</v>
       </c>
       <c r="F7" t="n">
-        <v>6.0905</v>
+        <v>5.9472</v>
       </c>
     </row>
     <row r="8">
@@ -603,7 +603,7 @@
         <v>4605.379883</v>
       </c>
       <c r="F8" t="n">
-        <v>7681.919922</v>
+        <v>7721.919922</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         <v>15498.389648</v>
       </c>
       <c r="F9" t="n">
-        <v>26216.0625</v>
+        <v>26448.109375</v>
       </c>
     </row>
     <row r="10">
@@ -647,7 +647,7 @@
         <v>35819.558594</v>
       </c>
       <c r="F10" t="n">
-        <v>52373.011719</v>
+        <v>52447.628906</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>1783.900024</v>
       </c>
       <c r="F11" t="n">
-        <v>4032.800049</v>
+        <v>4072.300049</v>
       </c>
     </row>
     <row r="12">
@@ -691,7 +691,7 @@
         <v>83.56999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>102.870003</v>
+        <v>100.040001</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>84.379997</v>
       </c>
       <c r="F13" t="n">
-        <v>111.949997</v>
+        <v>109.370003</v>
       </c>
     </row>
     <row r="14">
@@ -735,7 +735,7 @@
         <v>1235.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1248.5</v>
+        <v>1249.75</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +757,7 @@
         <v>568.25</v>
       </c>
       <c r="F15" t="n">
-        <v>454</v>
+        <v>451.5</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -471,7 +471,7 @@
         <v>103501</v>
       </c>
       <c r="F2" t="n">
-        <v>176027.578125</v>
+        <v>171106.125</v>
       </c>
     </row>
     <row r="3">
@@ -493,7 +493,7 @@
         <v>99.68000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>173.179993</v>
+        <v>168.339996</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>111.199997</v>
       </c>
       <c r="F4" t="n">
-        <v>100.730003</v>
+        <v>94.989998</v>
       </c>
     </row>
     <row r="5">
@@ -537,7 +537,7 @@
         <v>283</v>
       </c>
       <c r="F5" t="n">
-        <v>465.970001</v>
+        <v>469.320007</v>
       </c>
     </row>
     <row r="6">
@@ -559,7 +559,7 @@
         <v>5.6449</v>
       </c>
       <c r="F6" t="n">
-        <v>5.3271</v>
+        <v>5.3707</v>
       </c>
     </row>
     <row r="7">
@@ -581,7 +581,7 @@
         <v>6.593</v>
       </c>
       <c r="F7" t="n">
-        <v>5.9472</v>
+        <v>5.9943</v>
       </c>
     </row>
     <row r="8">
@@ -603,7 +603,7 @@
         <v>4605.379883</v>
       </c>
       <c r="F8" t="n">
-        <v>7721.919922</v>
+        <v>7734.149902</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         <v>15498.389648</v>
       </c>
       <c r="F9" t="n">
-        <v>26448.109375</v>
+        <v>26453.009766</v>
       </c>
     </row>
     <row r="10">
@@ -647,7 +647,7 @@
         <v>35819.558594</v>
       </c>
       <c r="F10" t="n">
-        <v>52447.628906</v>
+        <v>52486.179688</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>1783.900024</v>
       </c>
       <c r="F11" t="n">
-        <v>4072.300049</v>
+        <v>4051.699951</v>
       </c>
     </row>
     <row r="12">
@@ -691,7 +691,7 @@
         <v>83.56999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>100.040001</v>
+        <v>103.459999</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>84.379997</v>
       </c>
       <c r="F13" t="n">
-        <v>109.370003</v>
+        <v>112.5</v>
       </c>
     </row>
     <row r="14">
@@ -735,7 +735,7 @@
         <v>1235.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1249.75</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +757,7 @@
         <v>568.25</v>
       </c>
       <c r="F15" t="n">
-        <v>451.5</v>
+        <v>451.75</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -471,7 +471,7 @@
         <v>103501</v>
       </c>
       <c r="F2" t="n">
-        <v>171106.125</v>
+        <v>169332.734375</v>
       </c>
     </row>
     <row r="3">
@@ -493,7 +493,7 @@
         <v>99.68000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>168.339996</v>
+        <v>166.600006</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>111.199997</v>
       </c>
       <c r="F4" t="n">
-        <v>94.989998</v>
+        <v>93.900002</v>
       </c>
     </row>
     <row r="5">
@@ -537,7 +537,7 @@
         <v>283</v>
       </c>
       <c r="F5" t="n">
-        <v>469.320007</v>
+        <v>471</v>
       </c>
     </row>
     <row r="6">
@@ -559,7 +559,7 @@
         <v>5.6449</v>
       </c>
       <c r="F6" t="n">
-        <v>5.3707</v>
+        <v>5.4112</v>
       </c>
     </row>
     <row r="7">
@@ -581,7 +581,7 @@
         <v>6.593</v>
       </c>
       <c r="F7" t="n">
-        <v>5.9943</v>
+        <v>6.0453</v>
       </c>
     </row>
     <row r="8">
@@ -603,7 +603,7 @@
         <v>4605.379883</v>
       </c>
       <c r="F8" t="n">
-        <v>7734.149902</v>
+        <v>7711.899902</v>
       </c>
     </row>
     <row r="9">
@@ -612,21 +612,13 @@
           <t>nasdaq</t>
         </is>
       </c>
-      <c r="B9" s="1" t="n">
-        <v>44500</v>
-      </c>
-      <c r="C9" s="1" t="n">
-        <v>46326</v>
-      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>61</v>
-      </c>
-      <c r="E9" t="n">
-        <v>15498.389648</v>
-      </c>
-      <c r="F9" t="n">
-        <v>26453.009766</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -647,7 +639,7 @@
         <v>35819.558594</v>
       </c>
       <c r="F10" t="n">
-        <v>52486.179688</v>
+        <v>52266.71875</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +661,7 @@
         <v>1783.900024</v>
       </c>
       <c r="F11" t="n">
-        <v>4051.699951</v>
+        <v>4027.5</v>
       </c>
     </row>
     <row r="12">
@@ -691,7 +683,7 @@
         <v>83.56999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>103.459999</v>
+        <v>100.889999</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +705,7 @@
         <v>84.379997</v>
       </c>
       <c r="F13" t="n">
-        <v>112.5</v>
+        <v>109.889999</v>
       </c>
     </row>
     <row r="14">
@@ -735,7 +727,7 @@
         <v>1235.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1243</v>
+        <v>1235.5</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +749,7 @@
         <v>568.25</v>
       </c>
       <c r="F15" t="n">
-        <v>451.75</v>
+        <v>452.5</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -459,19 +459,19 @@
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="C2" s="1" t="n">
         <v>46326</v>
       </c>
       <c r="D2" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E2" t="n">
-        <v>103501</v>
+        <v>101915</v>
       </c>
       <c r="F2" t="n">
-        <v>169332.734375</v>
+        <v>168219.609375</v>
       </c>
     </row>
     <row r="3">
@@ -481,19 +481,19 @@
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="C3" s="1" t="n">
         <v>46326</v>
       </c>
       <c r="D3" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E3" t="n">
-        <v>99.68000000000001</v>
+        <v>98.349998</v>
       </c>
       <c r="F3" t="n">
-        <v>166.600006</v>
+        <v>165.490005</v>
       </c>
     </row>
     <row r="4">
@@ -503,19 +503,19 @@
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="C4" s="1" t="n">
         <v>46326</v>
       </c>
       <c r="D4" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E4" t="n">
-        <v>111.199997</v>
+        <v>108.800003</v>
       </c>
       <c r="F4" t="n">
-        <v>93.900002</v>
+        <v>91.81999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -525,19 +525,19 @@
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="C5" s="1" t="n">
         <v>46326</v>
       </c>
       <c r="D5" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E5" t="n">
-        <v>283</v>
+        <v>280.549988</v>
       </c>
       <c r="F5" t="n">
-        <v>471</v>
+        <v>465.75</v>
       </c>
     </row>
     <row r="6">
@@ -547,19 +547,19 @@
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="C6" s="1" t="n">
         <v>46326</v>
       </c>
       <c r="D6" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E6" t="n">
-        <v>5.6449</v>
+        <v>5.6007</v>
       </c>
       <c r="F6" t="n">
-        <v>5.4112</v>
+        <v>5.4297</v>
       </c>
     </row>
     <row r="7">
@@ -569,19 +569,19 @@
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="C7" s="1" t="n">
         <v>46326</v>
       </c>
       <c r="D7" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E7" t="n">
-        <v>6.593</v>
+        <v>6.3223</v>
       </c>
       <c r="F7" t="n">
-        <v>6.0453</v>
+        <v>6.0641</v>
       </c>
     </row>
     <row r="8">
@@ -591,19 +591,19 @@
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="C8" s="1" t="n">
         <v>46326</v>
       </c>
       <c r="D8" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E8" t="n">
-        <v>4605.379883</v>
+        <v>4567</v>
       </c>
       <c r="F8" t="n">
-        <v>7711.899902</v>
+        <v>7594.609863</v>
       </c>
     </row>
     <row r="9">
@@ -612,13 +612,21 @@
           <t>nasdaq</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
+      <c r="B9" s="1" t="n">
+        <v>44530</v>
+      </c>
+      <c r="C9" s="1" t="n">
+        <v>46326</v>
+      </c>
       <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="E9" t="n">
+        <v>15537.69043</v>
+      </c>
+      <c r="F9" t="n">
+        <v>25479.597656</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -627,19 +635,19 @@
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="C10" s="1" t="n">
         <v>46326</v>
       </c>
       <c r="D10" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E10" t="n">
-        <v>35819.558594</v>
+        <v>34483.71875</v>
       </c>
       <c r="F10" t="n">
-        <v>52266.71875</v>
+        <v>51957.371094</v>
       </c>
     </row>
     <row r="11">
@@ -649,19 +657,19 @@
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="C11" s="1" t="n">
         <v>46326</v>
       </c>
       <c r="D11" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E11" t="n">
-        <v>1783.900024</v>
+        <v>1773.599976</v>
       </c>
       <c r="F11" t="n">
-        <v>4027.5</v>
+        <v>3906</v>
       </c>
     </row>
     <row r="12">
@@ -671,19 +679,19 @@
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="C12" s="1" t="n">
         <v>46326</v>
       </c>
       <c r="D12" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E12" t="n">
-        <v>83.56999999999999</v>
+        <v>66.18000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>100.889999</v>
+        <v>104.360001</v>
       </c>
     </row>
     <row r="13">
@@ -693,19 +701,19 @@
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="C13" s="1" t="n">
         <v>46326</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E13" t="n">
-        <v>84.379997</v>
+        <v>70.56999999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>109.889999</v>
+        <v>113.879997</v>
       </c>
     </row>
     <row r="14">
@@ -715,19 +723,19 @@
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="C14" s="1" t="n">
         <v>46326</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E14" t="n">
-        <v>1235.75</v>
+        <v>1217.25</v>
       </c>
       <c r="F14" t="n">
-        <v>1235.5</v>
+        <v>1235.25</v>
       </c>
     </row>
     <row r="15">
@@ -737,19 +745,19 @@
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="C15" s="1" t="n">
         <v>46326</v>
       </c>
       <c r="D15" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E15" t="n">
-        <v>568.25</v>
+        <v>567</v>
       </c>
       <c r="F15" t="n">
-        <v>452.5</v>
+        <v>447.75</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -471,7 +471,7 @@
         <v>101915</v>
       </c>
       <c r="F2" t="n">
-        <v>168219.609375</v>
+        <v>167922</v>
       </c>
     </row>
     <row r="3">
@@ -493,7 +493,7 @@
         <v>98.349998</v>
       </c>
       <c r="F3" t="n">
-        <v>165.490005</v>
+        <v>165.399994</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>108.800003</v>
       </c>
       <c r="F4" t="n">
-        <v>91.81999999999999</v>
+        <v>92.150002</v>
       </c>
     </row>
     <row r="5">
@@ -537,7 +537,7 @@
         <v>280.549988</v>
       </c>
       <c r="F5" t="n">
-        <v>465.75</v>
+        <v>466.5</v>
       </c>
     </row>
     <row r="6">
@@ -559,7 +559,7 @@
         <v>5.6007</v>
       </c>
       <c r="F6" t="n">
-        <v>5.4297</v>
+        <v>5.3848</v>
       </c>
     </row>
     <row r="7">
@@ -581,7 +581,7 @@
         <v>6.3223</v>
       </c>
       <c r="F7" t="n">
-        <v>6.0641</v>
+        <v>6.0193</v>
       </c>
     </row>
     <row r="8">
@@ -603,7 +603,7 @@
         <v>4567</v>
       </c>
       <c r="F8" t="n">
-        <v>7594.609863</v>
+        <v>7580.069824</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         <v>15537.69043</v>
       </c>
       <c r="F9" t="n">
-        <v>25479.597656</v>
+        <v>25437</v>
       </c>
     </row>
     <row r="10">
@@ -647,7 +647,7 @@
         <v>34483.71875</v>
       </c>
       <c r="F10" t="n">
-        <v>51957.371094</v>
+        <v>51770.308594</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>1773.599976</v>
       </c>
       <c r="F11" t="n">
-        <v>3906</v>
+        <v>3898.899902</v>
       </c>
     </row>
     <row r="12">
@@ -691,7 +691,7 @@
         <v>66.18000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>104.360001</v>
+        <v>104.120003</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>70.56999999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>113.879997</v>
+        <v>117.639999</v>
       </c>
     </row>
     <row r="14">
@@ -735,7 +735,7 @@
         <v>1217.25</v>
       </c>
       <c r="F14" t="n">
-        <v>1235.25</v>
+        <v>1222.25</v>
       </c>
     </row>
     <row r="15">
